--- a/data/sutochno_report.xlsx
+++ b/data/sutochno_report.xlsx
@@ -567,9 +567,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>33.3</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>000001111000000111111111110110000000000001110000000000000000</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -577,7 +581,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -625,7 +629,11 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -633,7 +641,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -681,7 +689,11 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -689,7 +701,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -735,9 +747,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+        <v>33.3</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>111000001111000000000000001111110000000011110000000011100000</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -745,7 +761,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -793,7 +809,11 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -801,7 +821,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -849,7 +869,11 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -857,7 +881,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -903,9 +927,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
+        <v>71.7</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>111000011011000000001111111111110000111111111111111111111111</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -913,7 +941,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -961,7 +989,11 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -969,7 +1001,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -1015,9 +1047,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>111111100000011111111000000000001111111111111111111111110000</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1025,7 +1061,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -1071,9 +1107,13 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>111111111011111111000011111111110000000000110000111100000111</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1081,7 +1121,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -1127,9 +1167,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
+        <v>56.7</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>111100011111000000011111000000011111111111111111110000000001</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1137,7 +1181,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1229,11 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1193,7 +1241,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1289,11 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1249,7 +1301,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -1295,9 +1347,13 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
+        <v>28.3</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>111000001110000111110000000000000000000001111000001100000000</t>
+        </is>
+      </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1305,7 +1361,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1409,11 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1361,7 +1421,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1469,11 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1417,7 +1481,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -1463,9 +1527,13 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
+        <v>61.7</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>111111111111111111111111111110000000000000111111110000000000</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1473,7 +1541,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -1519,9 +1587,13 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
+        <v>76.7</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>111100011100001111111111111111111111100011111100111111100111</t>
+        </is>
+      </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1529,7 +1601,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1649,11 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1585,7 +1661,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -1626,9 +1702,13 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
+        <v>43.3</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>111000000000000000000000000000011111110000001111111111111111</t>
+        </is>
+      </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1636,7 +1716,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -1682,9 +1762,13 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
+        <v>95</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>111111111111111110111111111111111111111011111111111111110111</t>
+        </is>
+      </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1692,7 +1776,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -1738,9 +1822,13 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
+        <v>53.3</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>110000000000000000000111111110000011111111111111100001111111</t>
+        </is>
+      </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1748,7 +1836,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -1794,9 +1882,13 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>111110000111000000000000000001111111101111111000000011110000</t>
+        </is>
+      </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1804,7 +1896,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1944,11 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1860,7 +1956,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1999,11 @@
       <c r="K26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1911,7 +2011,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -1959,7 +2059,11 @@
       <c r="K27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1967,7 +2071,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -2008,9 +2112,13 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
+        <v>63.3</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>111000001111000000011011011111110001110011110111011111111110</t>
+        </is>
+      </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2018,7 +2126,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -2064,9 +2172,13 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>111111111111111111111111111111111111000011111111111100000111</t>
+        </is>
+      </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2074,7 +2186,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -2120,9 +2232,13 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
+        <v>75</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>111111111111111111111111111110000000000001111111111110011110</t>
+        </is>
+      </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2130,7 +2246,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -2176,9 +2292,13 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
+        <v>38.3</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>111111110000111111111111111000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2186,7 +2306,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -2232,9 +2352,13 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>111111111111111111111111111111111111111111111111111111111111</t>
+        </is>
+      </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2242,7 +2366,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2414,11 @@
       <c r="K33" t="n">
         <v>0</v>
       </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2298,7 +2426,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -2344,9 +2472,13 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
+        <v>71.7</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>111111111111111111111111111111110000000001111000111110000011</t>
+        </is>
+      </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2354,7 +2486,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -2400,9 +2532,13 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
+        <v>56.7</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>111000111100111001111111000011111111000000111111111000000000</t>
+        </is>
+      </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2410,7 +2546,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -2451,9 +2587,13 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>111011111111000000000111000000000001110000000111001111111111</t>
+        </is>
+      </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2461,7 +2601,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2649,11 @@
       <c r="K37" t="n">
         <v>0</v>
       </c>
-      <c r="L37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2517,7 +2661,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -2563,9 +2707,13 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>111100001110111101111111111111111000000001111000000011111111</t>
+        </is>
+      </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2573,7 +2721,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -2619,9 +2767,13 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="inlineStr"/>
+        <v>11.7</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>111100000000000000000000000000000000001110000000000000000000</t>
+        </is>
+      </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2629,7 +2781,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2829,11 @@
       <c r="K40" t="n">
         <v>0</v>
       </c>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2685,7 +2841,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -2731,9 +2887,13 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="inlineStr"/>
+        <v>46.7</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>111111111111101110000000000000000000000000011111111000001111</t>
+        </is>
+      </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2741,7 +2901,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -2787,9 +2947,13 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="inlineStr"/>
+        <v>95</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>111111110111111101111111111111111111111101111111111111111111</t>
+        </is>
+      </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2797,7 +2961,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -2843,9 +3007,13 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="inlineStr"/>
+        <v>61.7</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>111101111111110000000011111111111110000000000111111111110000</t>
+        </is>
+      </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2853,7 +3021,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -2899,9 +3067,13 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>111111111111000000000000011111111100001111111111111111111110</t>
+        </is>
+      </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2909,7 +3081,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -2955,9 +3127,13 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="inlineStr"/>
+        <v>43.3</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>111111111111111100111111111100000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2965,7 +3141,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -3011,9 +3187,13 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>111110000011110001111111111100111111111001110000000111111100</t>
+        </is>
+      </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -3021,7 +3201,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -3067,9 +3247,13 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>111111111111100000011111111111111111111111111100011111111111</t>
+        </is>
+      </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -3077,7 +3261,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3309,11 @@
       <c r="K48" t="n">
         <v>0</v>
       </c>
-      <c r="L48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -3133,7 +3321,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -3179,9 +3367,13 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>111000000111111111111111111111100000011111111111111000000111</t>
+        </is>
+      </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -3189,7 +3381,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -3235,9 +3427,13 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>111111111111001111111111111110111111000000111111000000000000</t>
+        </is>
+      </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -3245,7 +3441,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3489,11 @@
       <c r="K51" t="n">
         <v>0</v>
       </c>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -3301,7 +3501,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-05-01 14:07</t>
+          <t>2026-05-01 14:52</t>
         </is>
       </c>
     </row>

--- a/data/sutochno_report.xlsx
+++ b/data/sutochno_report.xlsx
@@ -540,37 +540,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2161386</t>
+          <t>1993982</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Уютная студия в апарт-комплексе Vertical We I Московская</t>
+          <t>Апартаменты студия</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2396</v>
+        <v>2250</v>
       </c>
       <c r="D2" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="E2" t="n">
-        <v>422</v>
+        <v>264</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Орджоникидзе улица, 44А</t>
+          <t>Санкт-Петербург, Политехническая улица, 6соор1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Московская ~24 мин. пешком</t>
+          <t>Площадь Мужества ~11 мин. пешком</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>4797</v>
+        <v>2925</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0;2420;2420;2420;2662;2662;4235;4235;4235;3630;3267;3267;3872;4477;4477;3267;3267;3872;3872;3872;4477;4477;3267;3267;3872;3872;3872;4477;4477;3267;4840;5445;7260;7260;7260;7260;4840;4840;5445;5445;5445;7260;7260;4840;4840;5445;5445;5445;6050;6050;4840;4840;5445;7260;7260;7260;7260;4840;4840;5445</t>
+          <t>2520;3330;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -601,29 +601,29 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>960363</t>
+          <t>959241</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Двухместные апартаменты у метро Площадь Восстания</t>
+          <t>Двухместный с 1 кроватью или 2 отдельными кроватями стандартный</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2422</v>
+        <v>2252</v>
       </c>
       <c r="D3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="E3" t="n">
-        <v>294</v>
+        <v>979</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
@@ -633,12 +633,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, 8-я Советская улица, 10</t>
+          <t>Санкт-Петербург, Казанская улица, 43</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Маяковская ~19 мин. пешком</t>
+          <t>Садовая ~9 мин. пешком</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -651,15 +651,15 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>000000000000000000000000000000</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>3076</v>
+        <v>5486</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2423;1986;1891;1995;1995;2090;2660;3515;3515;2565;2280;2280;2280;3515;3705;3135;3135;3325;3325;3325;3895;3990;3230;3230;3515;3515;3515;4180;4370;3895</t>
+          <t>2253;3800;3800;4200;4200;3800;5100;4400;3190;3190;3190;3290;5690;5790;3490;3490;3490;3690;3690;4790;5390;4190;4190;4190;4390;4390;5190;5390;4690;4790;6400;7200;7200;7800;7800;5690;5690;5990;5990;6990;7590;7590;6290;6290;6390;6390;6390;6890;6990;6190;6190;6190;6390;6390;7690;8190;7190;7190;7190;7490</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -669,44 +669,44 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:18</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1533075</t>
+          <t>1389133</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Двухместный номер с 2 отдельными кроватями эконом с видом на город</t>
+          <t>Уютные двухместные апартаменты в жк зум</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1400</v>
+        <v>2016</v>
       </c>
       <c r="D4" t="n">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="E4" t="n">
-        <v>217</v>
+        <v>345</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Рубинштейна улица, 32</t>
+          <t>Санкт-Петербург, Матроса Железняка улица, 2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Достоевская ~2 мин. пешком</t>
+          <t>Чёрная речка ~13 мин. пешком</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -715,19 +715,19 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>111111110000001111111111101100000000000011100000000000000000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2355</v>
+        <v>3216</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0;0;0;0;0;0;0;0;1502;0;1700;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;2355;2410;2432;2411;2472;2366;2333;2333;0;0;0;0;0;0;0;2444;2444;2444;2444;2444;2444;2444;2444;2444;2444;2440;2440;2440;2440;0;0;0</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -737,44 +737,44 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1224179</t>
+          <t>1688961</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Двухместный номер с 1 кроватью стандарт</t>
+          <t>Двухместный с 2 отдельными кроватями Стандарт, окна во внутренний двор/мансардные окна</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2500</v>
+        <v>2190</v>
       </c>
       <c r="D5" t="n">
-        <v>9.1</v>
+        <v>9.5</v>
       </c>
       <c r="E5" t="n">
-        <v>237</v>
+        <v>1549</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Прилукская улица, 21-23А</t>
+          <t>Санкт-Петербург, Большая Конюшенная улица, 25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Обводный Канал ~9 мин. пешком</t>
+          <t>Невский проспект ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -791,11 +791,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2500</v>
+        <v>6174</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500</t>
+          <t>0;2190;2190;2190;2990;3490;0;2990;2490;2490;3990;3990;5490;5490;2990;2990;5990;5990;7190;7190;7190;5490;5490;7190;5490;5490;5490;5490;5490;7190;5490;5490;5490;8990;7190;7190;5490;5490;5490;8990;10990;8990;5490;5490;8990;8990;8990;8990;8990;5490;5490;7190;7190;7190;8490;10990;10990;7190;7190;7190</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -805,44 +805,44 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>725023</t>
+          <t>2086533</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Двухместный с 2 отдельными кроватями студия двухместная с одной совместной или раздельными кроватями</t>
+          <t>Двухместный номер с 1 кроватью Бюджетный номер недалеко от Московского вокзала</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2475</v>
+        <v>2468</v>
       </c>
       <c r="D6" t="n">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>41</v>
+        <v>209</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Захарьевская улица, 21</t>
+          <t>Санкт-Петербург, Маяковского улица, 3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Чернышевская ~6 мин. пешком</t>
+          <t>Маяковская ~5 мин. пешком</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -855,15 +855,15 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>000000000000000000000000000000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>3996</v>
+        <v>2904</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0;2750;2750;2750;2750;2750;4950;4950;4950;3300;3300;3300;3300;0;0;0;3300;3300;3300;3300;4180;5005;4950;4950;4950;4950;4950;5005;5005;4950</t>
+          <t>2904</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -873,44 +873,44 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:18</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1557971</t>
+          <t>1904075</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Квартира комфорт класса с джакузи рядом с центром</t>
+          <t>Апартаменты студия возле московского вокзала + смарт тв</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>423</v>
+        <v>2243</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="E7" t="n">
-        <v>111</v>
+        <v>244</v>
       </c>
       <c r="F7" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Тосина улица, 6</t>
+          <t>Санкт-Петербург, Гончарная улица, 17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Обводный Канал ~24 мин. пешком</t>
+          <t>Площадь Восстания ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -919,19 +919,19 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>110000011111111000000000000000000000000000000000000000000000</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>13760</v>
+        <v>5667</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0;0;6041;6041;6041;6041;0;0;0;0;0;0;0;0;0;9063;9063;9063;9063;9063;9063;9063;9063;9566;10070;12084;14099;16113;16113;16113;16113;16113;16113;16113;16113;16113;16113;16113;16113;16113;16113;16113;16113;16113;16113;16113;16113;16113;16113;16113;16113;16113;16113;16113;16113;16113;16113;16113;16113;16113</t>
+          <t>0;2220;2220;2220;2220;4737;4737;3737;3857;3421;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4599;4599;5478;4980;4980;4980;4980;4980;4980;4980;4980;12144;12144;12144;12144;12144;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -941,44 +941,44 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1268089</t>
+          <t>1970296</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Номер-эконом в 3 минутах от метро Чернышевская</t>
+          <t>студия возле московского вокзала + смарт тв</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2444</v>
+        <v>2243</v>
       </c>
       <c r="D8" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>324</v>
+        <v>122</v>
       </c>
       <c r="F8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Фурштатская улица, 17</t>
+          <t>Санкт-Петербург, Гончарная улица, 10</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Чернышевская ~4 мин. пешком</t>
+          <t>Площадь Восстания ~9 мин. пешком</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -987,19 +987,19 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>26.7</v>
+        <v>0</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>100000000111100000000111000000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>2973</v>
+        <v>2244</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0;2375;2375;2375;2375;2375;0;0;0;0;0;0;0;3750;3562;3250;3125;3125;3125;3125;3562;0;0;0;3125;0;0;0;0;0</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1009,44 +1009,44 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1326063</t>
+          <t>960363</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Двухместный номер с 1 кроватью с ванной комнатой</t>
+          <t>Двухместные апартаменты у метро Площадь Восстания</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2250</v>
+        <v>1890</v>
       </c>
       <c r="D9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>336</v>
+        <v>294</v>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, 1-ая Советская улица, 12</t>
+          <t>Санкт-Петербург, 8-я Советская улица, 10</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~4 мин. пешком</t>
+          <t>Маяковская ~19 мин. пешком</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1063,11 +1063,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>2533</v>
+        <v>4130</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0;2500;2500;0;0;0;0;0;0;0;0;2500;2500;0;0;2500;0;0;2500;0;0;0;0;0;2500;2750;2750;2500;0;0;0;0;2500;2500;2500;0;0;0;0;0;2500;0;0;0;0;2500;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
+          <t>1986;1891;1995;1995;2090;2660;3515;3515;2565;2280;2280;2280;3515;3705;3135;3135;3325;3325;3325;3895;3990;3230;3230;3515;3515;3515;4180;4370;3895;3895;6166;6451;6451;6831;6831;3990;3990;4180;4180;6451;6831;6831;4456;4456;4551;4551;4551;4931;5026;4551;4551;4703;4703;4703;5216;5406;4551;4551;4703;4703</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1077,44 +1077,44 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1328593</t>
+          <t>1688970</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Двухместный номер с ванной комнатой</t>
+          <t>Семейный улучшенная комната, окна во внутренний двор/ мансардные окна.</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2338</v>
+        <v>2390</v>
       </c>
       <c r="D10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="E10" t="n">
-        <v>336</v>
+        <v>1549</v>
       </c>
       <c r="F10" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, 1-ая Советская улица, 12</t>
+          <t>Санкт-Петербург, Большая Конюшенная улица, 25</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~4 мин. пешком</t>
+          <t>Невский проспект ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1127,15 +1127,15 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>000000000000000000000000000000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>2550</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0;2500;2500;0;0;0;0;0;0;0;0;2500;2500;0;0;2500;0;0;2500;0;0;0;0;0;2500;2750;2750;2500;0;0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1145,44 +1145,44 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1557970</t>
+          <t>1726444</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Квартира комфорт класса с джакузи рядом с центром и метро</t>
+          <t>Двухместный с 1 кроватью классический</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1057</v>
+        <v>2090</v>
       </c>
       <c r="D11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1549</v>
+      </c>
+      <c r="F11" t="n">
         <v>10</v>
       </c>
-      <c r="E11" t="n">
-        <v>111</v>
-      </c>
-      <c r="F11" t="n">
-        <v>35</v>
-      </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Тосина улица, 6</t>
+          <t>Санкт-Петербург, Большая Конюшенная улица, 25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Обводный Канал ~24 мин. пешком</t>
+          <t>Невский проспект ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1191,19 +1191,19 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>110000011111111000000000000000000000000000000000000000000000</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>13614</v>
+        <v>6171</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0;0;5999;5999;5999;5999;0;0;0;0;0;0;0;0;0;8999;8999;8999;8999;8999;8999;8999;8999;9498;9998;11998;13999;15999;15999;15999;15999;15999;15999;15999;15999;15999;15999;15999;15999;15999;15999;15999;15999;0;15999;15999;15999;15999;15999;15999;15999;15999;15999;15999;15999;15999;15999;15999;15999;15999</t>
+          <t>0;2190;2090;2090;2990;3490;0;2990;2490;2490;3990;3990;5490;5490;2990;2990;5990;5990;7190;7190;7190;5490;5490;7190;5490;5490;5490;5490;5490;7190;5490;5490;5490;8990;7190;7190;5490;5490;5490;8990;10990;8990;5490;5490;8990;8990;8990;8990;8990;5490;5490;7190;7190;7190;8490;10990;10990;7190;7190;7190</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1213,29 +1213,29 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1976395</t>
+          <t>2175215</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Уютная студия возле метро</t>
+          <t>Двухместный номер с 2 отдельными кроватями Стандарт</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2160</v>
+        <v>2500</v>
       </c>
       <c r="D12" t="n">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="F12" t="n">
         <v>12</v>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Краснопутиловская улица, 105</t>
+          <t>Санкт-Петербург, Невский проспект, 95</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Московская ~12 мин. пешком</t>
+          <t>Площадь Восстания ~9 мин. пешком</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1259,19 +1259,19 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>86.7</v>
+        <v>0</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>100001111111111111111111111111</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>2467</v>
+        <v>2500</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0;2400;0;2500;2500;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1281,44 +1281,44 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2177842</t>
+          <t>911091</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Двухместный номер с 2 отдельными кроватями Стандарт</t>
+          <t>Двухместный номер с 1 кроватью стандарт</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="D13" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="E13" t="n">
-        <v>81</v>
+        <v>286</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Невский проспект, 117</t>
+          <t>Санкт-Петербург, Малый Васильевского Острова проспект, 46</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Площадь Александра Невского-2 ~11 мин. пешком</t>
+          <t>Василеостровская ~14 мин. пешком</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1327,19 +1327,19 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>000000000000000000000000000000000000000000000000000000000000</t>
+          <t>100000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>5589</v>
+        <v>4381</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2520;2500;3200;3200;3200;3200;4000;4000;4000;4000;4000;4000;4050;4150;4150;4100;4100;4100;4067;4033;4000;12600;12600;0;0;0;0;0;0;0;0;0;0;0;0;6500;6400;6500;6600;6600;6600;6600;6500;6400;6500;6600;7700;0;6600;6600;6600;6700;6800;6800;6700;6600;6500;6400;6500;6600</t>
+          <t>0;2500;2500;2500;2500;3000;4500;4500;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4800;4800;4800;4800;4800;4800;4800;4800;4800;4800;5100;5100;5200;4800;4800;4800;4800;4800;4800;4800;4800;4800;4800;4800;5100;5400;5400;5400;5000;5000;5000</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1349,44 +1349,44 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1623984</t>
+          <t>332218</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Двухместный номер с 1 кроватью и общими удобствами</t>
+          <t>Студия</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2300</v>
+        <v>2429</v>
       </c>
       <c r="D14" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>159</v>
+        <v>43</v>
       </c>
       <c r="F14" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Гончарная улица, 11А</t>
+          <t>Санкт-Петербург, Чайковского улица, 36</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~4 мин. пешком</t>
+          <t>Чернышевская ~4 мин. пешком</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1395,19 +1395,19 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>000000000000000000000000000000</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>2455</v>
+        <v>0</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0;1900;1500;1500;1500;1500;2100;2700;2700;2200;1700;1700;1700;1800;1900;1800;1700;1700;1700;1800;2800;3700;3700;3700;3700;3700;3700;3700;3700;3700</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1417,44 +1417,44 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1900294</t>
+          <t>1726461</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Уютная квартирка у метро Черная Речка и метро Пионерская</t>
+          <t>Двухместный с 2 отдельными кроватями классический</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2500</v>
+        <v>2090</v>
       </c>
       <c r="D15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="E15" t="n">
-        <v>23</v>
+        <v>1549</v>
       </c>
       <c r="F15" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Матроса Железняка улица, 35</t>
+          <t>Санкт-Петербург, Большая Конюшенная улица, 25</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Чёрная речка ~21 мин. пешком</t>
+          <t>Невский проспект ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>63.3</v>
+        <v>0</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>111111000000111111110000000000011111111111111111111111100000</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>3662</v>
+        <v>6192</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0;0;0;0;0;0;3450;3450;3450;3450;3450;0;0;0;0;0;0;0;0;0;3450;3450;3450;3450;3450;3450;3450;3450;3450;3450;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;4250;4250;4250;4250;4500</t>
+          <t>0;2190;2090;2090;2990;3490;0;3390;2490;2490;3990;3990;5490;5490;3390;3390;5990;5990;7190;7190;7190;5490;5490;7190;5490;5490;5490;5490;5490;7190;5490;5490;5490;8990;7190;7190;5490;5490;5490;8990;10990;8990;5490;5490;8990;8990;8990;8990;8990;5490;5490;7190;7190;7190;8490;10990;10990;7190;7190;7190</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -1485,44 +1485,44 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>581753</t>
+          <t>691455</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Уютная студия у Московского вокзала</t>
+          <t>Двухместный с 1 кроватью апартамент стандарт с двуспальной кроватью</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2450</v>
+        <v>2300</v>
       </c>
       <c r="D16" t="n">
-        <v>9.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>133</v>
+        <v>832</v>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Лиговский проспект, 51</t>
+          <t>Санкт-Петербург, 12-я Красноармейская улица, 14/16</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~2 мин. пешком</t>
+          <t>Балтийская ~12 мин. пешком</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1531,19 +1531,19 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>36.7</v>
+        <v>0</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>100000000001100001111000001111</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>5000</v>
+        <v>2588</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0;0;0;0;0;0;0;5000;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1553,44 +1553,44 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1942545</t>
+          <t>2174887</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Квартира у моря - 1</t>
+          <t>Двухместный номер с 2 отдельными кроватями Эконом</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2380</v>
+        <v>2200</v>
       </c>
       <c r="D17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E17" t="n">
         <v>74</v>
       </c>
       <c r="F17" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="G17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Ленинский проспект, 57к1</t>
+          <t>Санкт-Петербург, Невский проспект, 130</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Юго-Западная ~42 мин. пешком</t>
+          <t>Площадь Восстания ~5 мин. пешком</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1599,19 +1599,19 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>56.7</v>
+        <v>0</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>111000111110000000111110000000111111111111111111100000000011</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>2773</v>
+        <v>4359</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0;0;0;2300;2300;0;0;0;0;0;0;2390;2390;2390;2390;2390;2390;0;0;0;0;0;0;2690;2690;2690;2690;2690;2690;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;3190;3190;3190;3190;3190;3190;3190;3190;3190;0;0</t>
+          <t>2200;2800;2800;2800;2800;3100;3100;2500;2800;2800;2800;2800;2800;2800;2800;2800;2900;3000;3100;3000;2900;2800;2875;2950;3025;3100;3425;4175;0;5760;6100;5980;5860;5740;5620;0;5620;5740;5740;5740;0;5620;5500;5620;5740;5740;5740;5740;5740;5740;5860;5980;5980;5860;5740;5620;5500;5620;5740;5740</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -1621,44 +1621,44 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>482183</t>
+          <t>691477</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Двухместная уютная комната в центре Санкт-Петербурга</t>
+          <t>Апартаменты малые с двуспальной кроватью</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1600</v>
+        <v>2070</v>
       </c>
       <c r="D18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>385</v>
+        <v>832</v>
       </c>
       <c r="F18" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G18" t="n">
         <v>2</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Загородный проспект, 12</t>
+          <t>Санкт-Петербург, 12-я Красноармейская улица, 14/16</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Владимирская ~4 мин. пешком</t>
+          <t>Балтийская ~12 мин. пешком</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1671,15 +1671,15 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>000000000000000000000000000000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>2272</v>
+        <v>2588</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0;1790;2060;2095;2130;2130;2550;2370;2310;2360;2215;2300;2300;2330;2315;2300;2300;2300;2300;2300;2330;2315;2300;2300;2300;2300;2300;2330;2330;2330</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -1689,44 +1689,44 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1095355</t>
+          <t>933305</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Капюшон студия</t>
+          <t>Апартаменты светлая студия</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2500</v>
+        <v>2258</v>
       </c>
       <c r="D19" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="E19" t="n">
-        <v>104</v>
+        <v>2228</v>
       </c>
       <c r="F19" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Лиговский проспект, 193</t>
+          <t>Санкт-Петербург, Гривцова переулок, 24</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Обводный Канал ~4 мин. пешком</t>
+          <t>Садовая ~2 мин. пешком</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1735,19 +1735,19 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>88.3</v>
+        <v>0</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>111111111110011111111111111111111111000111111110011111111111</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>3583</v>
+        <v>8686</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0;0;0;0;0;0;0;0;0;0;0;2000;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;3750;0;0;0;0;0;0;0;0;0;0;5000;0;0;0;0;0;0;0;0;0;0;0;0</t>
+          <t>4059;4711;4845;4845;4912;6252;8028;7492;5046;5046;5046;5046;7056;7056;6855;6855;6855;6855;7056;7257;7056;6855;6654;6855;6855;6855;10239;10038;9234;9234;12852;12852;12852;12852;10306;9502;9502;9770;9770;12450;12852;13254;9435;9435;9770;9770;9770;10306;10306;9502;9770;9770;9770;9502;12852;13254;9435;9502;9435;9703</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -1757,44 +1757,44 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:18</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1779585</t>
+          <t>1688940</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Двухместный с 1 кроватью с кухонной зоной в шаговой доступности от Эрмитажа</t>
+          <t>Двухместный с 1 кроватью Стандартная комната, окна во внутренний двор/ мансардные окна.</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1800</v>
+        <v>2190</v>
       </c>
       <c r="D20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="E20" t="n">
-        <v>187</v>
+        <v>1549</v>
       </c>
       <c r="F20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G20" t="n">
         <v>2</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Моховая улица, 30</t>
+          <t>Санкт-Петербург, Большая Конюшенная улица, 25</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Чернышевская ~14 мин. пешком</t>
+          <t>Невский проспект ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1807,15 +1807,15 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>000000000000000000000000000000000000000000000000000000000000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>2556</v>
+        <v>0</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0;0;0;0;0;0;1700;1600;1500;1500;1500;1500;1500;1500;1500;1500;1500;1675;2075;2475;2500;2300;2400;2700;3000;2767;2533;2233;2400;2567;2800;2800;2883;2967;3050;2967;2883;2800;2800;2883;2967;3050;2967;2883;2800;2800;2883;2967;3050;2967;2883;2800;2800;3138;3475;3813;3475;3138;2900;3000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -1825,44 +1825,44 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:18</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>952023</t>
+          <t>602947</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Комната</t>
+          <t>Двухместный номер с 1 кроватью стандарт</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1980</v>
+        <v>2284</v>
       </c>
       <c r="D21" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="E21" t="n">
-        <v>253</v>
+        <v>650</v>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G21" t="n">
         <v>2</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Старо-Петергофский проспект, 52</t>
+          <t>Санкт-Петербург, 7-я Красноармейская улица, 5</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Нарвская ~1 мин. пешком</t>
+          <t>Технологический институт-1 ~8 мин. пешком</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1871,19 +1871,19 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>000000000011110000011000000000</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>1956</v>
+        <v>5836</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0;1800;1800;1800;2000;2000;2000;0;0;1600;0;0;0;0;0;0;1800;0;1800;0;0;2300;2000;2000;2000;2000;2000;2000;2500;1800</t>
+          <t>3589;2488;2488;2738;2938;4488;4489;4988;4488;4488;4488;4488;4988;4988;4238;4238;4238;4238;4238;4988;4988;4238;4238;4238;4238;4238;5488;5488;4813;6113;7988;7189;7526;7864;6964;6738;6738;6738;6738;7738;7864;7132;7113;7113;7113;7113;7113;7863;7863;7113;7113;7113;7113;7113;8613;8613;7113;7113;7113;7113</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -1893,44 +1893,44 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:18</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1965177</t>
+          <t>986915</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Семейный номер в мини отеле в центре города</t>
+          <t>Апартаменты атмосферная студия</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1400</v>
+        <v>2499</v>
       </c>
       <c r="D22" t="n">
         <v>9.5</v>
       </c>
       <c r="E22" t="n">
-        <v>130</v>
+        <v>2228</v>
       </c>
       <c r="F22" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Караванная улица, 14</t>
+          <t>Санкт-Петербург, Гривцова переулок, 24</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Гостиный двор ~9 мин. пешком</t>
+          <t>Садовая ~2 мин. пешком</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1943,15 +1943,15 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>000000000000000000000000000000000000000000000000000000000000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>4998</v>
+        <v>4059</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0;1400;0;0;0;0;2500;0;0;2500;2500;2500;2500;0;3000;0;0;3000;0;0;0;0;3000;3000;3000;0;0;0;0;4500;4500;6000;6000;6000;6000;6000;6000;6000;6000;6000;6000;0;0;6000;6000;6000;6000;6000;6000;6000;6000;6000;6000;6000;6000;6000;6000;6000;6000;6000</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -1961,44 +1961,44 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:18</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025035</t>
+          <t>1543516</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Трёхместный номер</t>
+          <t>Двухместный номер с 1 кроватью улучшенный</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="D23" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>177</v>
+        <v>275</v>
       </c>
       <c r="F23" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, 1-ая Советская улица, 12</t>
+          <t>Санкт-Петербург, 9-я Советская улица, 5А</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~4 мин. пешком</t>
+          <t>Площадь Восстания ~15 мин. пешком</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2011,15 +2011,15 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>000000000000000000000000000000</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>2658</v>
+        <v>6410</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0;2200;2300;2300;2300;3000;3200;0;0;2300;2300;2300;2300;2400;0;2500;2400;2400;2400;2500;2700;3000;2700;2800;3000;3000;3000;3000;3400;3400</t>
+          <t>2500;2800;2800;2800;2800;3900;3900;3900;3900;3900;4150;4700;5000;4800;4600;4600;4600;4600;4600;4600;4600;4600;4600;4800;5000;5200;6075;6900;7725;8580;8700;8580;8460;8340;8220;8100;8220;8340;8340;8340;8340;8220;8100;8220;8340;8340;8340;8340;8220;8100;8220;8340;8340;0;8340;8220;8100;8220;8340;8340</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2029,44 +2029,44 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>971489</t>
+          <t>995419</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Видовая квартира на 11 этаже, у метро</t>
+          <t>Двухместный с 1 кроватью стандарт</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="D24" t="n">
-        <v>9.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>160</v>
+        <v>978</v>
       </c>
       <c r="F24" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="G24" t="n">
         <v>2</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Маршала Жукова проспект, 41</t>
+          <t>Санкт-Петербург, Гороховая улица, 34</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Проспект Ветеранов ~30 мин. пешком</t>
+          <t>Сенная площадь ~4 мин. пешком</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2075,19 +2075,19 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>38.3</v>
+        <v>0</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>000000111000000111111110000000111100000111111110000000000000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>3467</v>
+        <v>2300</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0;2500;2500;2500;2500;0;0;0;0;3000;3000;3000;3000;3000;0;0;0;0;0;0;0;0;0;3000;3000;3000;3000;3000;0;0;0;0;0;0;4000;4000;4000;0;0;0;0;0;0;0;0;0;0;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -2097,44 +2097,44 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2058859</t>
+          <t>1640654</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Двушка у Нарвской - уют, игры, 5 минут до метро</t>
+          <t>Двухместный номер с 1 кроватью улучшенный</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>500</v>
+        <v>1700</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="E25" t="n">
-        <v>39</v>
+        <v>461</v>
       </c>
       <c r="F25" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Метростроевцев улица, 2</t>
+          <t>Санкт-Петербург, Малая Посадская улица, 12</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Нарвская ~8 мин. пешком</t>
+          <t>Горьковская ~7 мин. пешком</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2143,19 +2143,19 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>110111110001111111000001111111</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>4455</v>
+        <v>3059</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0;0;4433;0;0;0;0;0;4533;4400;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
+          <t>2000;1700;1700;1700;2000;3000;0;0;1800;1800;1900;1900;2000;2050;2000;2000;2000;2000;2000;2500;2700;2500;2500;2500;2700;2800;2950;2950;2700;3000;3000;3150;3425;3550;3425;3300;3300;3500;3950;4200;4200;3950;3700;3700;3700;3950;4200;4200;4200;4200;4200;4200;4200;4075;3950;3825;3700;3700;3700;3750</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -2165,44 +2165,44 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>706393</t>
+          <t>1957263</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Видовая квартира на 15 этаже, у метро</t>
+          <t>Шикарная студия в стиле Boho</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2500</v>
+        <v>1943</v>
       </c>
       <c r="D26" t="n">
-        <v>9.9</v>
+        <v>9.4</v>
       </c>
       <c r="E26" t="n">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="F26" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G26" t="n">
         <v>2</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Маршала Жукова проспект, 41</t>
+          <t>Санкт-Петербург, Витебский улица, 99к1</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Проспект Ветеранов ~30 мин. пешком</t>
+          <t>Купчино ~4 мин. пешком</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2211,19 +2211,19 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>100000111100000000111111000000000000000111111111110000000011</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>3383</v>
+        <v>0</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0;2500;2500;2500;2500;0;0;0;0;0;3000;3000;3000;3000;3000;3000;3000;0;0;0;0;0;0;0;3000;3000;3000;3000;3000;3500;4000;4000;4000;4000;4000;4000;4000;0;0;0;0;0;0;0;0;0;0;0;0;0;4000;4000;4000;4000;4000;4000;0;0;0;0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -2233,44 +2233,44 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1639737</t>
+          <t>2177201</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Апартаменты рядом с метро</t>
+          <t>Двухместный номер с 2 отдельными кроватями Стандарт</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2400</v>
+        <v>2240</v>
       </c>
       <c r="D27" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>28</v>
+        <v>221</v>
       </c>
       <c r="F27" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G27" t="n">
         <v>2</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Матроса Железняка улица, 2с1</t>
+          <t>Санкт-Петербург, Невский проспект, 147</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Чёрная речка ~16 мин. пешком</t>
+          <t>Площадь Александра Невского-2 ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2279,19 +2279,19 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>111111111111111111111111111100000000000001111111100000000000</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>4486</v>
+        <v>5194</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;5300;5300;4400;4400;4400;4400;4400;4400;4400;4400;0;0;0;0;0;0;0;0;0;0;0;4400;4400;4400;4400;4400;4400;4400;4400;4400;4400;4400</t>
+          <t>2240;3300;3300;3300;3300;3300;3900;3300;3300;3300;3300;3600;3900;3600;3300;3300;3300;3500;3700;3700;3500;3300;3300;3575;3850;4225;5125;5750;6375;6900;6900;6800;6700;6600;6500;6400;6500;6600;6600;6600;6600;6500;6400;6500;6600;6600;6600;6600;6600;6600;6700;6800;6800;6700;6600;6500;6400;6500;6600;6600</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -2301,44 +2301,44 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>554939</t>
+          <t>938089</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Семейный Двухуровневый</t>
+          <t>Апартаменты Стандарт</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1500</v>
+        <v>2300</v>
       </c>
       <c r="D28" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>263</v>
+        <v>700</v>
       </c>
       <c r="F28" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G28" t="n">
         <v>2</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Кирочная улица, 12</t>
+          <t>Санкт-Петербург, Биржевой переулок, 1/10</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Чернышевская ~5 мин. пешком</t>
+          <t>Василеостровская ~13 мин. пешком</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2351,15 +2351,15 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>000000000000000000000000000000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>2059</v>
+        <v>0</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0;1900;1900;1900;1300;1900;1900;1400;1200;1200;1200;1300;1600;1907;2113;2120;2120;2120;2213;2307;2433;2467;2500;2500;2633;2767;2900;2767;2633;2500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -2369,44 +2369,44 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>927531</t>
+          <t>950985</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Уютная квартира с отдельным входом</t>
+          <t>Эконом с двумя кроватями</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2500</v>
+        <v>1901</v>
       </c>
       <c r="D29" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="E29" t="n">
-        <v>148</v>
+        <v>620</v>
       </c>
       <c r="F29" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Выборгское шоссе, 23к2</t>
+          <t>Санкт-Петербург, Коломенская улица, 14</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Проспект Просвещения ~37 мин. пешком</t>
+          <t>Лиговский проспект ~7 мин. пешком</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2415,19 +2415,19 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>76.7</v>
+        <v>0</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>111000111000011111111111111111111111000111111001111111001111</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>2500</v>
+        <v>2435</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0;0;0;2500;2500;0;0;0;0;2500;2500;2500;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;2500;2500;0;0;0;0;0;0;0;2500;0;0;0;0;0;0;0;0;2500;2500;0;0;0;0</t>
+          <t>1901;1901;1901;1901;1901;2201;2201;2201;1901;1901;1901;1901;1901;1901;1901;1901;1901;1901;1901;3101;0;2701;2701;2701;2701;2701;2901;2901;7700;2701;2701;2701;2701;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -2437,39 +2437,44 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2034830</t>
+          <t>956337</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Уютная студия в Красносельском районе</t>
+          <t>Апартаменты стандарт</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>10</v>
+        <v>340</v>
       </c>
       <c r="F30" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G30" t="n">
         <v>2</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Ветеранов проспект, 204</t>
+          <t>Санкт-Петербург, Лиговский проспект, 80</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Лиговский проспект ~1 мин. пешком</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2478,19 +2483,19 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>111111100000011111111111111111</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>2450</v>
+        <v>0</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0;0;0;0;0;0;0;2500;2500;2467;2433;2400;2400;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -2500,44 +2505,44 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1688666</t>
+          <t>1224179</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Апартаменты на Лесной</t>
+          <t>Двухместный номер с 1 кроватью стандарт</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>2500</v>
       </c>
       <c r="D31" t="n">
-        <v>9.9</v>
+        <v>9.1</v>
       </c>
       <c r="E31" t="n">
-        <v>135</v>
+        <v>237</v>
       </c>
       <c r="F31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Большой Сампсониевский проспект, 74к2</t>
+          <t>Санкт-Петербург, Прилукская улица, 21-23А</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Лесная ~10 мин. пешком</t>
+          <t>Обводный Канал ~9 мин. пешком</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2546,19 +2551,19 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>111111111111111101111111111111111111110111111111111111101111</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;2700;0;0;0;0</t>
+          <t>2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -2568,44 +2573,44 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1784361</t>
+          <t>725023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Comfort Loft на Лиговском</t>
+          <t>Двухместный с 2 отдельными кроватями студия двухместная с одной совместной или раздельными кроватями</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2500</v>
+        <v>2475</v>
       </c>
       <c r="D32" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="E32" t="n">
-        <v>518</v>
+        <v>41</v>
       </c>
       <c r="F32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G32" t="n">
         <v>2</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Пушкинская улица, 12</t>
+          <t>Санкт-Петербург, Захарьевская улица, 21</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~5 мин. пешком</t>
+          <t>Чернышевская ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2618,15 +2623,15 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>000000000000000000000000000000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>2410</v>
+        <v>2475</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0;2950;2500;1800;1800;1950;0;0;0;2000;2000;2300;2700;0;0;2300;2100;2100;2350;2650;2600;2550;2500;2600;2500;2500;2500;2500;2700;3400</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -2636,44 +2641,44 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>551249</t>
+          <t>1986647</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Двухместный номер с 1 кроватью комната в квартире</t>
+          <t>Шикарная дизайнерская студия</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1850</v>
+        <v>2057</v>
       </c>
       <c r="D33" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>175</v>
+        <v>24</v>
       </c>
       <c r="F33" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G33" t="n">
         <v>2</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Гороховая улица, 66</t>
+          <t>Санкт-Петербург, Витебский проспект, 99к1</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Пушкинская ~4 мин. пешком</t>
+          <t>Купчино ~4 мин. пешком</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2682,19 +2687,19 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>51.7</v>
+        <v>20</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>100000000000000000001111111100000111111111111111000011111110</t>
+          <t>110000000011111111000000110000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>1796</v>
+        <v>5813</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0;1850;1850;1850;1830;1810;1790;1770;1750;1750;1750;1750;1750;1750;1750;1750;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;1979</t>
+          <t>0;0;3429;3429;3429;4064;4572;4572;4318;0;0;0;0;0;0;0;0;0;4572;4572;4572;4572;4572;0;0;0;4572;4572;4572;5842;7112;8382;8382;7112;5842;5842;5842;5842;5842;5842;5842;5842;5842;5842;5842;5842;5842;6414;6985;6985;6985;6985;6985;6985;6985;6985;6985;6985;6985;6985</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -2704,44 +2709,44 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>978781</t>
+          <t>1957240</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>трехместный (TRIPLE)</t>
+          <t>Уютная студия в 5 минутах от аэропорта</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1890</v>
+        <v>1943</v>
       </c>
       <c r="D34" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F34" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Захарьевская улица, 14В</t>
+          <t>Санкт-Петербург, Витебский проспект, 99к1</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Чернышевская ~6 мин. пешком</t>
+          <t>Купчино ~4 мин. пешком</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2750,19 +2755,19 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>100000000000000000000000000000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>2677</v>
+        <v>0</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0;1784;2339;2620;2869;3118;2900;2682;2464;2246;2246;0;0;0;0;0;0;0;0;0;0;3742;3118;0;0;0;0;0;0;0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -2772,44 +2777,44 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1728559</t>
+          <t>1957286</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Двухместный номер с 1 кроватью эконом</t>
+          <t>Видовая студия в ЖК Интуит</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1400</v>
+        <v>1943</v>
       </c>
       <c r="D35" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>124</v>
+        <v>25</v>
       </c>
       <c r="F35" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="G35" t="n">
         <v>2</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Тележная улица, 1/6</t>
+          <t>Санкт-Петербург, Витебский проспект, 101к1</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Площадь Александра Невского-2 ~10 мин. пешком</t>
+          <t>Купчино ~3 мин. пешком</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2818,19 +2823,19 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1.7</v>
+        <v>10</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>100000000000000000000000000000000000000000000000000000000000</t>
+          <t>110110110000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>1768</v>
+        <v>5404</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0;0;2300;1600;1600;2300;2500;2500;1900;1400;1300;1300;1300;1300;2000;1300;1300;1700;1700;1700;1500;1500;1500;1500;2000;2500;2000;2000;2000;2000;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
+          <t>0;0;0;0;0;0;0;0;4191;3683;3937;3937;3937;3937;3937;3937;3937;3937;4318;4318;4318;4318;4318;4318;4318;4318;4318;4318;4318;5842;7112;8382;8382;7112;5842;5842;5842;5842;5842;5842;5842;5842;5842;5842;5842;5842;5842;6096;6350;6350;6350;6350;6350;6350;6350;6350;6350;6350;6350;0</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -2840,44 +2845,44 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2194910</t>
+          <t>2161386</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Квартира у моря -3</t>
+          <t>Уютная студия в апарт-комплексе Vertical We I Московская</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2242</v>
+        <v>2420</v>
       </c>
       <c r="D36" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="E36" t="n">
-        <v>24</v>
+        <v>422</v>
       </c>
       <c r="F36" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="G36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Ленинский проспект, 68</t>
+          <t>Санкт-Петербург, Орджоникидзе улица, 44А</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Юго-Западная ~43 мин. пешком</t>
+          <t>Московская ~24 мин. пешком</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2886,19 +2891,19 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>56.7</v>
+        <v>0</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>111111011111110000000111100000</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>2658</v>
+        <v>4808</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;2590;2590;2590;2590;2590;2590;2670;0;0;0;0;2790;2790;2790;0;0</t>
+          <t>2420;2420;2420;2662;2662;4235;4235;4235;3630;3267;3267;3872;4477;4477;3267;3267;3872;3872;3872;4477;4477;3267;3267;3872;3872;3872;4477;4477;3267;4840;5445;7260;7260;7260;7260;4840;4840;5445;5445;5445;7260;7260;4840;4840;5445;5445;5445;6050;6050;4840;4840;5445;7260;7260;7260;7260;4840;4840;5445;5445</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -2908,44 +2913,44 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:18</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1821359</t>
+          <t>935949</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Уютная студия в историческом центре</t>
+          <t>Апартаменты уютный</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2400</v>
+        <v>2375</v>
       </c>
       <c r="D37" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="F37" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G37" t="n">
         <v>2</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Невский проспект, 168Г</t>
+          <t>Санкт-Петербург, 11-я Васильевского острова линия, 18В</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Площадь Александра Невского-1 ~7 мин. пешком</t>
+          <t>Василеостровская ~11 мин. пешком</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2954,19 +2959,19 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>100000111100000000000011111110000000000000000000000000000000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>4615</v>
+        <v>2375</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0;2280;2280;2280;2280;0;0;0;0;0;2878;2850;2850;2850;2850;2850;2850;2850;2850;2850;2850;0;0;0;0;0;0;0;0;3990;5510;5890;6270;6270;5966;5586;5206;5130;5510;5890;6270;6270;5890;5510;5130;5130;5320;5510;5510;5320;5130;5130;5130;5510;5890;6270;5890;5510;5130;5130</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -2976,44 +2981,44 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:18</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1689789</t>
+          <t>2086576</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Апартаменты улучшенный</t>
+          <t>Двухместный номер с 1 кроватью Классический номер на Рубинштейна</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2430</v>
+        <v>2420</v>
       </c>
       <c r="D38" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="E38" t="n">
-        <v>72</v>
+        <v>233</v>
       </c>
       <c r="F38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G38" t="n">
         <v>2</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, На Турухтанные Острова дорога, 5к1</t>
+          <t>Санкт-Петербург, Рубинштейна улица, 30</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Автово ~10 мин. пешком</t>
+          <t>Достоевская ~1 мин. пешком</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3026,15 +3031,15 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>000000000000000000000000000000</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>3872</v>
+        <v>5379</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0;3400;3760;3760;3760;3760;3760;4660;3760;3760;3760;3760;3760;3760;4660;3760;3760;3760;3760;3760;3760;4660;3760;3760;3760;3760;3760;3760;4660;3760</t>
+          <t>2420;2420;2553;2553;2723;5324;5324;4840;4356;4356;4356;4356;4840;4840;4235;4235;4356;4356;4356;4961;4961;4235;4235;4356;4356;4356;5324;5324;4598;5445;6050;7502;7502;7502;7502;5445;5445;6050;0;6413;7502;7502;5445;5445;6050;6050;6050;7502;7502;5445;5445;6050;7502;7502;7502;7502;5445;5445;6050;6050</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -3044,39 +3049,44 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:18</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1012379</t>
+          <t>937649</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Комната</t>
+          <t>Двухместный номер с 1 кроватью стандарт</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1600</v>
+        <v>1900</v>
       </c>
       <c r="D39" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="E39" t="n">
-        <v>158</v>
+        <v>1769</v>
       </c>
       <c r="F39" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G39" t="n">
         <v>2</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Владимирский проспект, 10</t>
+          <t>Санкт-Петербург, Садовая улица, 28-30к2</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Гостиный двор ~7 мин. пешком</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3085,19 +3095,19 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>61.7</v>
+        <v>0</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>110000011110000000110110111111100011100111101110111111111100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>1867</v>
+        <v>1900</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0;0;1600;1600;1600;1600;0;0;0;0;0;1600;1600;1600;1600;1600;1600;0;0;0;0;0;0;0;0;0;0;0;0;0;0;2400;2400;0;0;0;0;2400;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;2400;2400</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -3107,44 +3117,44 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:18</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1243341</t>
+          <t>2046531</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Студия эконом</t>
+          <t>Мансарда эконом</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2062</v>
+        <v>1901</v>
       </c>
       <c r="D40" t="n">
         <v>9.6</v>
       </c>
       <c r="E40" t="n">
-        <v>104</v>
+        <v>620</v>
       </c>
       <c r="F40" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Лиговский проспект, 193</t>
+          <t>Санкт-Петербург, Коломенская улица, 14</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Обводный Канал ~4 мин. пешком</t>
+          <t>Лиговский проспект ~7 мин. пешком</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3153,19 +3163,19 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>111110000111111111111000001111</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>2248</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
+          <t>1901;1901;1901;1901;1901;1901;2201;1901;1901;1901;1901;1901;1901;1901;1901;1901;1901;1901;1901;3101;0;2701;2701;2701;2701;2701;2701;2701;2701;2701;2701;2701;2701;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -3175,44 +3185,44 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1608009</t>
+          <t>1728294</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Двухместный номер с 1 кроватью стандартный номер с удобствами на этаже</t>
+          <t>Новая студия в ЖК In2it</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2500</v>
+        <v>1943</v>
       </c>
       <c r="D41" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="F41" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G41" t="n">
         <v>2</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Белы Куна улица, 16Б</t>
+          <t>Санкт-Петербург, Витебский проспект, 99к1</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Международная ~6 мин. пешком</t>
+          <t>Купчино ~4 мин. пешком</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3221,19 +3231,19 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>100000000000000000000000000000000000000000000000000000000000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>2639</v>
+        <v>0</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;3500;3500;3500;3500;3500;2700;2700;2700;2700;2700;2700;2700;2700;2700;2700;2700;2700;2700;2700;2700;2700</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -3243,44 +3253,44 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1344789</t>
+          <t>1904081</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Уютная студия рядом с метро</t>
+          <t>Апартаменты студия возле московского вокзала + смарт тв</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2500</v>
+        <v>2243</v>
       </c>
       <c r="D42" t="n">
-        <v>9.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>29</v>
+        <v>219</v>
       </c>
       <c r="F42" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Матроса Железняка улица, 2</t>
+          <t>Санкт-Петербург, Гончарная улица, 11А</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Чёрная речка ~13 мин. пешком</t>
+          <t>Площадь Восстания ~4 мин. пешком</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3289,19 +3299,19 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>53.3</v>
+        <v>0</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>000000000011111111111100111100</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>5400</v>
+        <v>6251</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;5400;5400</t>
+          <t>0;0;0;0;2220;4737;0;3737;3857;3421;4181;4181;4181;0;4181;4181;4181;0;0;0;0;4181;4181;0;4181;4181;4181;0;4599;6300;5727;5727;5727;5727;5727;5727;5727;5727;12144;12144;12144;12144;12144;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -3311,44 +3321,44 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1741448</t>
+          <t>803069</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Студия</t>
+          <t>Комфортная студия рядом с метро Площадь Мужества</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2500</v>
+        <v>2380</v>
       </c>
       <c r="D43" t="n">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>15</v>
+        <v>1516</v>
       </c>
       <c r="F43" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Обручевых улица, 5</t>
+          <t>Санкт-Петербург, Политехническая улица, 6</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Политехническая ~10 мин. пешком</t>
+          <t>Площадь Мужества ~12 мин. пешком</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3357,19 +3367,19 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>43.3</v>
+        <v>0</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>111111111111111111111111110000000000000000000000000000000000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>5700</v>
+        <v>4180</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;5340;5660;5567;5474;5660;5846;5753;5660;5660;5567;5581;5885;6188;6095;6002;5894;5684;5474;5660;5846;5753;5660;5660;5567;5474;5660;5846;5753;0;0;5567;5474;5660;5846</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -3379,44 +3389,44 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>999805</t>
+          <t>2015794</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Комната</t>
+          <t>Номер с двуспальной кроватью</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2500</v>
+        <v>2100</v>
       </c>
       <c r="D44" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>312</v>
+      </c>
+      <c r="F44" t="n">
         <v>10</v>
       </c>
-      <c r="E44" t="n">
-        <v>25</v>
-      </c>
-      <c r="F44" t="n">
-        <v>18</v>
-      </c>
       <c r="G44" t="n">
         <v>2</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Гатчинская улица, 1/56</t>
+          <t>Санкт-Петербург, Невский проспект, 136В</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Чкаловская ~11 мин. пешком</t>
+          <t>Площадь Восстания ~10 мин. пешком</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3425,19 +3435,19 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>111111111111111111111111111111</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>4307</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
+          <t>2100;2100;2300;2300;2200;2500;3500;2900;1600;1700;1800;2000;2300;3200;2300;2300;2300;2300;2500;3000;3500;2500;2900;2900;2900;2900;3000;4600;4000;4000;4600;4600;4600;5200;6300;4600;4600;5800;5800;5800;9200;9200;5800;5800;5800;5800;5800;6900;8100;5200;5200;5800;5800;5800;5800;6900;5800;5800;5800;5800</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -3447,44 +3457,44 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2021034</t>
+          <t>1901577</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Двухместный на Советской</t>
+          <t>Двухместный с 1 кроватью атмосферная комната</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2100</v>
+        <v>2416</v>
       </c>
       <c r="D45" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>177</v>
+        <v>121</v>
       </c>
       <c r="F45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G45" t="n">
         <v>2</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, 1-ая Советская улица, 12</t>
+          <t>Санкт-Петербург, реки Фонтанки набережная, 101</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~4 мин. пешком</t>
+          <t>Сенная площадь ~7 мин. пешком</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3493,19 +3503,19 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>100000000000000000000000000000000000000000000000000000000000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>3262</v>
+        <v>2416</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0;2200;2100;2100;2100;3000;3200;0;0;2300;2300;2300;2300;2400;0;2500;2400;2400;2400;2500;2600;3200;2700;2800;3000;3000;3000;3000;3400;3300;3850;3800;3850;4175;0;0;0;3800;3800;3850;0;0;4125;4000;4000;4000;4200;4400;4200;0;0;4400;4300;0;0;4125;3925;4000;4000;4000</t>
+          <t>2416</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -3515,44 +3525,44 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>600993</t>
+          <t>1533075</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Студия у метро</t>
+          <t>Двухместный номер с 2 отдельными кроватями эконом с видом на город</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2450</v>
+        <v>1400</v>
       </c>
       <c r="D46" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="E46" t="n">
-        <v>105</v>
+        <v>217</v>
       </c>
       <c r="F46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G46" t="n">
         <v>2</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Лиговский проспект, 55/4</t>
+          <t>Санкт-Петербург, Рубинштейна улица, 32</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~3 мин. пешком</t>
+          <t>Достоевская ~2 мин. пешком</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3561,19 +3571,19 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>3.3</v>
+        <v>38.3</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>100000000000000000000000000000</t>
+          <t>111111100000011111111111011000000000000111000000000000000000</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>2762</v>
+        <v>2355</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>0;2450;0;0;0;0;0;0;0;2800;2800;0;0;0;0;0;0;0;0;0;0;0;0;0;3000;0;0;0;0;0</t>
+          <t>0;0;0;0;0;0;0;1502;0;1700;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;2355;2410;2432;2411;2472;2366;2333;2333;0;0;0;0;0;0;0;2444;2444;2444;2444;2444;2444;2444;2444;2444;2444;2440;2440;2440;2440;0;0;0;0</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -3583,44 +3593,44 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1083531</t>
+          <t>1552905</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Студия Ваш Питер с бесконтактным заездом, хранением багажа, рядом с метро</t>
+          <t>Апартаменты в центре города у метро Площадь Восстания</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2000</v>
+        <v>1986</v>
       </c>
       <c r="D47" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>58</v>
+        <v>294</v>
       </c>
       <c r="F47" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G47" t="n">
         <v>2</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, реки Фонтанки набережная, 89</t>
+          <t>Санкт-Петербург, 8-я Советская улица, 10</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Спасская ~6 мин. пешком</t>
+          <t>Маяковская ~19 мин. пешком</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3629,19 +3639,19 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>111111111111100111111111111111100000000000011111100000011111</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>6443</v>
+        <v>4746</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;6200;6200;6450;6450;6450;6200;6200;6625;7050;0;0;0;0;0;0;0;0;0;6733;6400;6400;6400;0;0;0;0;0;0;0</t>
+          <t>1986;2138;2185;2185;2375;3135;4370;4370;3040;2660;2660;2660;4275;4465;3705;3705;3895;3895;3895;4465;4655;3791;3791;4076;4076;4076;4741;4940;4465;4465;6926;7401;7401;7781;7781;4465;4465;4655;4655;7401;7781;7781;5026;5026;5216;5216;5216;5691;5786;5216;5216;5406;5406;5406;5881;6166;5216;5216;5406;5406</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -3651,44 +3661,44 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>348617</t>
+          <t>1637686</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Оранжевая квартира с балконом</t>
+          <t>Апартаменты стандарт</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2300</v>
+        <v>2100</v>
       </c>
       <c r="D48" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E48" t="n">
-        <v>115</v>
+        <v>237</v>
       </c>
       <c r="F48" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="G48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Дрезденская улица, 10к1</t>
+          <t>Санкт-Петербург, Столярный переулок, 9</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Удельная ~13 мин. пешком</t>
+          <t>Садовая ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3697,19 +3707,19 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>111111111111111111111111111111101111111111110001111100000111</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;3500;0;0;0;0;0;0;0;3500;3500;3500;0;0;0;0;0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
@@ -3719,39 +3729,44 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1012673</t>
+          <t>1784360</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Комната</t>
+          <t>Standard Loft на Лиговском</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="D49" t="n">
-        <v>9.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>148</v>
+        <v>521</v>
       </c>
       <c r="F49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G49" t="n">
         <v>2</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Владимирский проспект, 10</t>
+          <t>Санкт-Петербург, Пушкинская улица, 12</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Площадь Восстания ~5 мин. пешком</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3760,19 +3775,19 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>110111111110000000001110000000000011100000001110011111111111</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>1904</v>
+        <v>3358</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>0;0;0;0;0;0;0;0;0;0;0;1600;1600;1600;1600;1600;1600;1600;1600;0;0;0;0;1600;1600;1600;1600;1600;1600;1600;2000;2400;2400;0;0;0;0;2400;2400;2400;2400;2400;2400;0;0;0;0;2400;0;0;0;0;0;0;0;0;0;0;0;0</t>
+          <t>1700;2300;1700;1800;1850;0;0;0;1900;1900;1900;2700;0;0;1800;2100;2100;2350;2550;2600;2550;2500;2500;2500;2500;2500;2500;2700;3400;3850;3850;3900;3950;3950;3900;3700;3700;3700;3750;3950;7700;4500;4300;3700;4050;4400;4400;4400;4400;4400;4400;4400;4400;4400;4400;4050;3700;3850;3850;3900</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
@@ -3782,44 +3797,44 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1468869</t>
+          <t>945839</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Двухкомнатная квартира в историческом центре Петербурга</t>
+          <t>Двухместный с 1 кроватью стандарт</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2354</v>
+        <v>2401</v>
       </c>
       <c r="D50" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="E50" t="n">
-        <v>103</v>
+        <v>620</v>
       </c>
       <c r="F50" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Канала Грибоедова набережная, 148</t>
+          <t>Санкт-Петербург, Коломенская улица, 14</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Садовая ~25 мин. пешком</t>
+          <t>Лиговский проспект ~7 мин. пешком</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3828,19 +3843,19 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>111111111111011101111110000000000000000000111111110000011110</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>7046</v>
+        <v>2401</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;3766;4237;4354;4590;3060;5296;6120;7650;7650;7650;7650;8827;8827;8239;8239;8239;8239;8239;0;0;0;0;0;0;0;0;0;8239;8239;8239;8239;0;0;0;0;0;8239</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
@@ -3850,44 +3865,44 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1052377</t>
+          <t>945957</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Светлая студия в центре</t>
+          <t>Двухместный номер с 1 кроватью стандарт</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>600</v>
+        <v>2375</v>
       </c>
       <c r="D51" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>19</v>
+        <v>125</v>
       </c>
       <c r="F51" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G51" t="n">
         <v>2</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, 5-я Красноармейская улица, 17</t>
+          <t>Санкт-Петербург, Невский проспект, 102</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Технологический институт-1 ~9 мин. пешком</t>
+          <t>Маяковская ~2 мин. пешком</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3900,15 +3915,15 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>000000000000000000000000000000</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>3973</v>
+        <v>7027</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0;3600;3600;3600;3600;4300;5000;5000;4900;4800;4800;0;4800;5050;5300;4350;3400;3400;3400;3400;3400;3400;3400;3400;3400;3400;3400;3400;3400;4350</t>
+          <t>2375;2660;3800;2850;2850;5225;6650;4750;3800;3800;5700;4750;6650;6175;5700;5700;5700;6650;6650;6650;6175;5700;5700;5700;5700;7600;6650;6175;5700;8360;8360;8930;8360;10355;10830;8835;8360;8360;8360;9025;0;9405;8835;8360;8360;8360;8360;8360;8835;8835;8360;8360;8360;8360;8360;8835;8835;8360;8360;8360</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
@@ -3918,7 +3933,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-05-02 19:05</t>
+          <t>2026-05-03 08:19</t>
         </is>
       </c>
     </row>

--- a/data/sutochno_report.xlsx
+++ b/data/sutochno_report.xlsx
@@ -540,37 +540,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1993982</t>
+          <t>709383</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Апартаменты студия</t>
+          <t>Апартаменты двухуровневый стандарт трехместный</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2250</v>
+        <v>5040</v>
       </c>
       <c r="D2" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>264</v>
+        <v>583</v>
       </c>
       <c r="F2" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Политехническая улица, 6соор1</t>
+          <t>Санкт-Петербург, Владимирский проспект, 16</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Площадь Мужества ~11 мин. пешком</t>
+          <t>Владимирская ~3 мин. пешком</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -581,19 +581,11 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>000000000000000000000000000000000000000000000000000000000000</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>2925</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2520;3330;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -601,44 +593,44 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-03 08:18</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>959241</t>
+          <t>760745</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Двухместный с 1 кроватью или 2 отдельными кроватями стандартный</t>
+          <t>Апартаменты двухуровневая студия для двоих у Восстания</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2252</v>
+        <v>4950</v>
       </c>
       <c r="D3" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>979</v>
+        <v>512</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Казанская улица, 43</t>
+          <t>Санкт-Петербург, Лиговский проспект, 75</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Садовая ~9 мин. пешком</t>
+          <t>Лиговский проспект ~7 мин. пешком</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -655,11 +647,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>5486</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2253;3800;3800;4200;4200;3800;5100;4400;3190;3190;3190;3290;5690;5790;3490;3490;3490;3690;3690;4790;5390;4190;4190;4190;4390;4390;5190;5390;4690;4790;6400;7200;7200;7800;7800;5690;5690;5990;5990;6990;7590;7590;6290;6290;6390;6390;6390;6890;6990;6190;6190;6190;6390;6390;7690;8190;7190;7190;7190;7490</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -669,44 +661,44 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-03 08:18</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1389133</t>
+          <t>1346585</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Уютные двухместные апартаменты в жк зум</t>
+          <t>Студия в стиле Лофт</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2016</v>
+        <v>5247</v>
       </c>
       <c r="D4" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="E4" t="n">
-        <v>345</v>
+        <v>1529</v>
       </c>
       <c r="F4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Матроса Железняка улица, 2</t>
+          <t>Санкт-Петербург, Гривцова переулок, 24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Чёрная речка ~13 мин. пешком</t>
+          <t>Садовая ~2 мин. пешком</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -719,15 +711,15 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>3216</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -737,44 +729,44 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-03 08:18</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1688961</t>
+          <t>1498426</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Двухместный с 2 отдельными кроватями Стандарт, окна во внутренний двор/мансардные окна</t>
+          <t>Атмосферная двухкомнатная квартира в центре</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2190</v>
+        <v>6587</v>
       </c>
       <c r="D5" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="E5" t="n">
-        <v>1549</v>
+        <v>1529</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Большая Конюшенная улица, 25</t>
+          <t>Санкт-Петербург, Гривцова переулок, 24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Невский проспект ~6 мин. пешком</t>
+          <t>Садовая ~2 мин. пешком</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -791,11 +783,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>6174</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0;2190;2190;2190;2990;3490;0;2990;2490;2490;3990;3990;5490;5490;2990;2990;5990;5990;7190;7190;7190;5490;5490;7190;5490;5490;5490;5490;5490;7190;5490;5490;5490;8990;7190;7190;5490;5490;5490;8990;10990;8990;5490;5490;8990;8990;8990;8990;8990;5490;5490;7190;7190;7190;8490;10990;10990;7190;7190;7190</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -805,44 +797,44 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-03 08:18</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2086533</t>
+          <t>955145</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Двухместный номер с 1 кроватью Бюджетный номер недалеко от Московского вокзала</t>
+          <t>Студия в апарт-комплексе "Салют" на Звездной</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2468</v>
+        <v>2239</v>
       </c>
       <c r="D6" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="E6" t="n">
-        <v>209</v>
+        <v>307</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Маяковского улица, 3</t>
+          <t>Санкт-Петербург, Пулковское шоссе, 14с6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Маяковская ~5 мин. пешком</t>
+          <t>Звёздная ~17 мин. пешком</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -855,15 +847,15 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2904</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -873,44 +865,44 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-03 08:18</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1904075</t>
+          <t>935949</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Апартаменты студия возле московского вокзала + смарт тв</t>
+          <t>Апартаменты уютный</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2243</v>
+        <v>2850</v>
       </c>
       <c r="D7" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>244</v>
+        <v>370</v>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Гончарная улица, 17</t>
+          <t>Санкт-Петербург, 11-я Васильевского острова линия, 18В</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~6 мин. пешком</t>
+          <t>Василеостровская ~11 мин. пешком</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -927,11 +919,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>5667</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0;2220;2220;2220;2220;4737;4737;3737;3857;3421;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4599;4599;5478;4980;4980;4980;4980;4980;4980;4980;4980;12144;12144;12144;12144;12144;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -941,44 +933,44 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1970296</t>
+          <t>581825</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>студия возле московского вокзала + смарт тв</t>
+          <t>Апартаменты двухуровневая студия стандарт</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2243</v>
+        <v>3750</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="E8" t="n">
-        <v>122</v>
+        <v>298</v>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Гончарная улица, 10</t>
+          <t>Санкт-Петербург, Лиговский проспект, 65</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~9 мин. пешком</t>
+          <t>Площадь Восстания ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -991,15 +983,15 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>2244</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1009,44 +1001,44 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>960363</t>
+          <t>1328239</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Двухместные апартаменты у метро Площадь Восстания</t>
+          <t>Семейная студия</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1890</v>
+        <v>5917</v>
       </c>
       <c r="D9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="E9" t="n">
-        <v>294</v>
+        <v>2228</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, 8-я Советская улица, 10</t>
+          <t>Санкт-Петербург, Гривцова переулок, 24</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Маяковская ~19 мин. пешком</t>
+          <t>Садовая ~2 мин. пешком</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1063,11 +1055,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>4130</v>
+        <v>0</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1986;1891;1995;1995;2090;2660;3515;3515;2565;2280;2280;2280;3515;3705;3135;3135;3325;3325;3325;3895;3990;3230;3230;3515;3515;3515;4180;4370;3895;3895;6166;6451;6451;6831;6831;3990;3990;4180;4180;6451;6831;6831;4456;4456;4551;4551;4551;4931;5026;4551;4551;4703;4703;4703;5216;5406;4551;4551;4703;4703</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1077,44 +1069,44 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1688970</t>
+          <t>1942433</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Семейный улучшенная комната, окна во внутренний двор/ мансардные окна.</t>
+          <t>Классическая студия в апарт-комплексе WELL на Балтийской</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2390</v>
+        <v>3988</v>
       </c>
       <c r="D10" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>1549</v>
+        <v>426</v>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Большая Конюшенная улица, 25</t>
+          <t>Санкт-Петербург, Измайловский бульвар, 1к2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Невский проспект ~6 мин. пешком</t>
+          <t>Балтийская ~8 мин. пешком</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1127,7 +1119,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -1135,7 +1127,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1145,44 +1137,44 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1726444</t>
+          <t>1904863</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Двухместный с 1 кроватью классический</t>
+          <t>Апартаменты стандарт</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2090</v>
+        <v>2880</v>
       </c>
       <c r="D11" t="n">
         <v>9.5</v>
       </c>
       <c r="E11" t="n">
-        <v>1549</v>
+        <v>849</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Большая Конюшенная улица, 25</t>
+          <t>Санкт-Петербург, Сердобольская улица, 7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Невский проспект ~6 мин. пешком</t>
+          <t>Чёрная речка ~20 мин. пешком</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1199,11 +1191,11 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>6171</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0;2190;2090;2090;2990;3490;0;2990;2490;2490;3990;3990;5490;5490;2990;2990;5990;5990;7190;7190;7190;5490;5490;7190;5490;5490;5490;5490;5490;7190;5490;5490;5490;8990;7190;7190;5490;5490;5490;8990;10990;8990;5490;5490;8990;8990;8990;8990;8990;5490;5490;7190;7190;7190;8490;10990;10990;7190;7190;7190</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1213,44 +1205,44 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2175215</t>
+          <t>521465</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Двухместный номер с 2 отдельными кроватями Стандарт</t>
+          <t>Студия</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2500</v>
+        <v>2999</v>
       </c>
       <c r="D12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="E12" t="n">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="F12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Невский проспект, 95</t>
+          <t>Санкт-Петербург, Полтавская улица, 5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~9 мин. пешком</t>
+          <t>Площадь Восстания ~7 мин. пешком</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1259,19 +1251,19 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>56.7</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>110000111001111111000111110000000011000011111011111000011111</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1281,44 +1273,44 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>911091</t>
+          <t>1666187</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Двухместный номер с 1 кроватью стандарт</t>
+          <t>Компактная студия New Horizon А5 для двоих у метро Сенная</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2500</v>
+        <v>3750</v>
       </c>
       <c r="D13" t="n">
         <v>9.5</v>
       </c>
       <c r="E13" t="n">
-        <v>286</v>
+        <v>425</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Малый Васильевского Острова проспект, 46</t>
+          <t>Санкт-Петербург, Апраксин переулок, 5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Василеостровская ~14 мин. пешком</t>
+          <t>Сенная площадь ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1327,19 +1319,19 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>100000000000000000000000000000000000000000000000000000000000</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>4381</v>
+        <v>0</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0;2500;2500;2500;2500;3000;4500;4500;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4000;4800;4800;4800;4800;4800;4800;4800;4800;4800;4800;5100;5100;5200;4800;4800;4800;4800;4800;4800;4800;4800;4800;4800;4800;5100;5400;5400;5400;5000;5000;5000</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1349,44 +1341,44 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>332218</t>
+          <t>1904075</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Студия</t>
+          <t>Апартаменты студия возле московского вокзала + смарт тв</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2429</v>
+        <v>2220</v>
       </c>
       <c r="D14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="E14" t="n">
-        <v>43</v>
+        <v>244</v>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Чайковского улица, 36</t>
+          <t>Санкт-Петербург, Гончарная улица, 17</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Чернышевская ~4 мин. пешком</t>
+          <t>Площадь Восстания ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1395,11 +1387,11 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M14" t="n">
@@ -1407,7 +1399,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1417,44 +1409,44 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1726461</t>
+          <t>1562447</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Двухместный с 2 отдельными кроватями классический</t>
+          <t>Шикарная студия</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2090</v>
+        <v>4912</v>
       </c>
       <c r="D15" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="E15" t="n">
-        <v>1549</v>
+        <v>77</v>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Большая Конюшенная улица, 25</t>
+          <t>Санкт-Петербург, Реки Фонтанки набережная, 110</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Невский проспект ~6 мин. пешком</t>
+          <t>Технологический институт-2 ~8 мин. пешком</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1463,19 +1455,19 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>000000000000000000000000000000000000000000000000000000000000</t>
+          <t>110000000111000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>6192</v>
+        <v>0</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0;2190;2090;2090;2990;3490;0;3390;2490;2490;3990;3990;5490;5490;3390;3390;5990;5990;7190;7190;7190;5490;5490;7190;5490;5490;5490;5490;5490;7190;5490;5490;5490;8990;7190;7190;5490;5490;5490;8990;10990;8990;5490;5490;8990;8990;8990;8990;8990;5490;5490;7190;7190;7190;8490;10990;10990;7190;7190;7190</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -1485,44 +1477,44 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>691455</t>
+          <t>1728294</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Двухместный с 1 кроватью апартамент стандарт с двуспальной кроватью</t>
+          <t>Новая студия в ЖК In2it</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2300</v>
+        <v>3048</v>
       </c>
       <c r="D16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>832</v>
+        <v>31</v>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, 12-я Красноармейская улица, 14/16</t>
+          <t>Санкт-Петербург, Витебский проспект, 99к1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Балтийская ~12 мин. пешком</t>
+          <t>Купчино ~4 мин. пешком</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1531,19 +1523,19 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>110000000001110000000001110000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>2588</v>
+        <v>0</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1553,44 +1545,44 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2174887</t>
+          <t>1471473</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Двухместный номер с 2 отдельными кроватями Эконом</t>
+          <t>Студия в апарт-комплексе Best Western Zoom</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2200</v>
+        <v>2783</v>
       </c>
       <c r="D17" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="F17" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Невский проспект, 130</t>
+          <t>Санкт-Петербург, Матроса Железняка улица, 2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~5 мин. пешком</t>
+          <t>Чёрная речка ~13 мин. пешком</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1601,19 +1593,11 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>000000000000000000000000000000000000000000000000000000000000</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
-        <v>4359</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2200;2800;2800;2800;2800;3100;3100;2500;2800;2800;2800;2800;2800;2800;2800;2800;2900;3000;3100;3000;2900;2800;2875;2950;3025;3100;3425;4175;0;5760;6100;5980;5860;5740;5620;0;5620;5740;5740;5740;0;5620;5500;5620;5740;5740;5740;5740;5740;5740;5860;5980;5980;5860;5740;5620;5500;5620;5740;5740</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1621,44 +1605,44 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>691477</t>
+          <t>788541</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Апартаменты малые с двуспальной кроватью</t>
+          <t>Апартаменты студио</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2070</v>
+        <v>3480</v>
       </c>
       <c r="D18" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>832</v>
+        <v>630</v>
       </c>
       <c r="F18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G18" t="n">
         <v>2</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, 12-я Красноармейская улица, 14/16</t>
+          <t>Санкт-Петербург, Гончарная улица, 8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Балтийская ~12 мин. пешком</t>
+          <t>Площадь Восстания ~4 мин. пешком</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1671,15 +1655,15 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>2588</v>
+        <v>0</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -1689,44 +1673,44 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>933305</t>
+          <t>942269</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Апартаменты светлая студия</t>
+          <t>Апартаменты студия</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2258</v>
+        <v>4550</v>
       </c>
       <c r="D19" t="n">
         <v>9.5</v>
       </c>
       <c r="E19" t="n">
-        <v>2228</v>
+        <v>3033</v>
       </c>
       <c r="F19" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Гривцова переулок, 24</t>
+          <t>Санкт-Петербург, Детский переулок, 2</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Садовая ~2 мин. пешком</t>
+          <t>Московские ворота ~4 мин. пешком</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1743,11 +1727,11 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>8686</v>
+        <v>0</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>4059;4711;4845;4845;4912;6252;8028;7492;5046;5046;5046;5046;7056;7056;6855;6855;6855;6855;7056;7257;7056;6855;6654;6855;6855;6855;10239;10038;9234;9234;12852;12852;12852;12852;10306;9502;9502;9770;9770;12450;12852;13254;9435;9435;9770;9770;9770;10306;10306;9502;9770;9770;9770;9502;12852;13254;9435;9502;9435;9703</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -1757,44 +1741,44 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-03 08:18</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1688940</t>
+          <t>977025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Двухместный с 1 кроватью Стандартная комната, окна во внутренний двор/ мансардные окна.</t>
+          <t>Атмосферная студия 5 в историческом центре</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2190</v>
+        <v>4644</v>
       </c>
       <c r="D20" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="E20" t="n">
-        <v>1549</v>
+        <v>1059</v>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G20" t="n">
         <v>2</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Большая Конюшенная улица, 25</t>
+          <t>Санкт-Петербург, Можайская улица, 28</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Невский проспект ~6 мин. пешком</t>
+          <t>Пушкинская ~10 мин. пешком</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1807,7 +1791,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M20" t="n">
@@ -1815,7 +1799,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -1825,44 +1809,44 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-05-03 08:18</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>602947</t>
+          <t>2087207</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Двухместный номер с 1 кроватью стандарт</t>
+          <t>Уютная двухуровневая студия в центре Петербурга</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2284</v>
+        <v>2239</v>
       </c>
       <c r="D21" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>650</v>
+        <v>299</v>
       </c>
       <c r="F21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, 7-я Красноармейская улица, 5</t>
+          <t>Санкт-Петербург, Курляндская улица, 6-8</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Технологический институт-1 ~8 мин. пешком</t>
+          <t>Балтийская ~13 мин. пешком</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1871,19 +1855,19 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>51.7</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>000000000000000000000000000000000000000000000000000000000000</t>
+          <t>000000000000000000000000000001111111111111111111111111111111</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>5836</v>
+        <v>0</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>3589;2488;2488;2738;2938;4488;4489;4988;4488;4488;4488;4488;4988;4988;4238;4238;4238;4238;4238;4988;4988;4238;4238;4238;4238;4238;5488;5488;4813;6113;7988;7189;7526;7864;6964;6738;6738;6738;6738;7738;7864;7132;7113;7113;7113;7113;7113;7863;7863;7113;7113;7113;7113;7113;8613;8613;7113;7113;7113;7113</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -1893,44 +1877,44 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-05-03 08:18</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>986915</t>
+          <t>1942400</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Апартаменты атмосферная студия</t>
+          <t>Студия с диваном в апарт-комплексе well на Балтийской</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2499</v>
+        <v>2692</v>
       </c>
       <c r="D22" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>2228</v>
+        <v>426</v>
       </c>
       <c r="F22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G22" t="n">
         <v>2</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Гривцова переулок, 24</t>
+          <t>Санкт-Петербург, Измайловский бульвар, 1к2</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Садовая ~2 мин. пешком</t>
+          <t>Балтийская ~8 мин. пешком</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1943,15 +1927,15 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>4059</v>
+        <v>0</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -1961,44 +1945,44 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-05-03 08:18</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1543516</t>
+          <t>880365</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Двухместный номер с 1 кроватью улучшенный</t>
+          <t>Дизайнерский апартамент категории studio</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2500</v>
+        <v>4200</v>
       </c>
       <c r="D23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>275</v>
+        <v>137</v>
       </c>
       <c r="F23" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G23" t="n">
         <v>2</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, 9-я Советская улица, 5А</t>
+          <t>Санкт-Петербург, Заозёрная улица, 3к3</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~15 мин. пешком</t>
+          <t>Фрунзенская ~9 мин. пешком</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2015,11 +1999,11 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>6410</v>
+        <v>0</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2500;2800;2800;2800;2800;3900;3900;3900;3900;3900;4150;4700;5000;4800;4600;4600;4600;4600;4600;4600;4600;4600;4600;4800;5000;5200;6075;6900;7725;8580;8700;8580;8460;8340;8220;8100;8220;8340;8340;8340;8340;8220;8100;8220;8340;8340;8340;8340;8220;8100;8220;8340;8340;0;8340;8220;8100;8220;8340;8340</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2029,44 +2013,44 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>995419</t>
+          <t>1389133</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Двухместный с 1 кроватью стандарт</t>
+          <t>Уютные двухместные апартаменты в жк зум</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2300</v>
+        <v>3300</v>
       </c>
       <c r="D24" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="E24" t="n">
-        <v>978</v>
+        <v>345</v>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G24" t="n">
         <v>2</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Гороховая улица, 34</t>
+          <t>Санкт-Петербург, Матроса Железняка улица, 2</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Сенная площадь ~4 мин. пешком</t>
+          <t>Чёрная речка ~13 мин. пешком</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2079,15 +2063,15 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -2097,44 +2081,44 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1640654</t>
+          <t>1425651</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Двухместный номер с 1 кроватью улучшенный</t>
+          <t>Апартаменты двухуровневые стандарт</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1700</v>
+        <v>5849</v>
       </c>
       <c r="D25" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>461</v>
+        <v>172</v>
       </c>
       <c r="F25" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Малая Посадская улица, 12</t>
+          <t>Санкт-Петербург, Жуковского улица, 7-9</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Горьковская ~7 мин. пешком</t>
+          <t>Маяковская ~9 мин. пешком</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2151,11 +2135,11 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>3059</v>
+        <v>0</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2000;1700;1700;1700;2000;3000;0;0;1800;1800;1900;1900;2000;2050;2000;2000;2000;2000;2000;2500;2700;2500;2500;2500;2700;2800;2950;2950;2700;3000;3000;3150;3425;3550;3425;3300;3300;3500;3950;4200;4200;3950;3700;3700;3700;3950;4200;4200;4200;4200;4200;4200;4200;4075;3950;3825;3700;3700;3700;3750</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -2165,44 +2149,44 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1957263</t>
+          <t>784633</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Шикарная студия в стиле Boho</t>
+          <t>Апартаменты стандартная студия с кроватью King size</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1943</v>
+        <v>2880</v>
       </c>
       <c r="D26" t="n">
-        <v>9.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>57</v>
+        <v>329</v>
       </c>
       <c r="F26" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G26" t="n">
         <v>2</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Витебский улица, 99к1</t>
+          <t>Санкт-Петербург, Пулковское шоссе, 14с6</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Купчино ~4 мин. пешком</t>
+          <t>Звёздная ~17 мин. пешком</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2215,7 +2199,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M26" t="n">
@@ -2223,7 +2207,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -2233,44 +2217,44 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2177201</t>
+          <t>1942541</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Двухместный номер с 2 отдельными кроватями Стандарт</t>
+          <t>Уютная трехместная студия БомбФлат на Фонтанке</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2240</v>
+        <v>4912</v>
       </c>
       <c r="D27" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="E27" t="n">
-        <v>221</v>
+        <v>73</v>
       </c>
       <c r="F27" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Невский проспект, 147</t>
+          <t>Санкт-Петербург, реки Фонтанки набережная, 94</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Площадь Александра Невского-2 ~6 мин. пешком</t>
+          <t>Пушкинская ~7 мин. пешком</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2287,11 +2271,11 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>5194</v>
+        <v>0</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2240;3300;3300;3300;3300;3300;3900;3300;3300;3300;3300;3600;3900;3600;3300;3300;3300;3500;3700;3700;3500;3300;3300;3575;3850;4225;5125;5750;6375;6900;6900;6800;6700;6600;6500;6400;6500;6600;6600;6600;6600;6500;6400;6500;6600;6600;6600;6600;6600;6600;6700;6800;6800;6700;6600;6500;6400;6500;6600;6600</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -2301,44 +2285,44 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>938089</t>
+          <t>1713953</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Апартаменты Стандарт</t>
+          <t>Двухместные апартаменты с раздельными кроватями и мини-кухней</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2300</v>
+        <v>3915</v>
       </c>
       <c r="D28" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="E28" t="n">
-        <v>700</v>
+        <v>975</v>
       </c>
       <c r="F28" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G28" t="n">
         <v>2</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Биржевой переулок, 1/10</t>
+          <t>Санкт-Петербург, Невский проспект, 90-92</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Василеостровская ~13 мин. пешком</t>
+          <t>Маяковская ~3 мин. пешком</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2351,7 +2335,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M28" t="n">
@@ -2359,7 +2343,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -2369,44 +2353,44 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>950985</t>
+          <t>944615</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Эконом с двумя кроватями</t>
+          <t>Студия у Московского вокзала</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1901</v>
+        <v>4590</v>
       </c>
       <c r="D29" t="n">
         <v>9.6</v>
       </c>
       <c r="E29" t="n">
-        <v>620</v>
+        <v>110</v>
       </c>
       <c r="F29" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G29" t="n">
         <v>2</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Коломенская улица, 14</t>
+          <t>Санкт-Петербург, Черняховского улица, 46</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Лиговский проспект ~7 мин. пешком</t>
+          <t>Лиговский проспект ~3 мин. пешком</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2423,11 +2407,11 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>2435</v>
+        <v>0</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1901;1901;1901;1901;1901;2201;2201;2201;1901;1901;1901;1901;1901;1901;1901;1901;1901;1901;1901;3101;0;2701;2701;2701;2701;2701;2901;2901;7700;2701;2701;2701;2701;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -2437,44 +2421,44 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>956337</t>
+          <t>578163</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Апартаменты стандарт</t>
+          <t>Апартаменты студия</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2300</v>
+        <v>2999</v>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>340</v>
+        <v>225</v>
       </c>
       <c r="F30" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G30" t="n">
         <v>2</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Лиговский проспект, 80</t>
+          <t>Санкт-Петербург, Полтавская улица, 5/29Б</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Лиговский проспект ~1 мин. пешком</t>
+          <t>Площадь Восстания ~10 мин. пешком</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2487,7 +2471,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M30" t="n">
@@ -2495,7 +2479,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -2505,44 +2489,44 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1224179</t>
+          <t>806761</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Двухместный номер с 1 кроватью стандарт</t>
+          <t>Современная студия в 10 минутах пешком от метро пл. Мужества</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2500</v>
+        <v>4460</v>
       </c>
       <c r="D31" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>237</v>
+        <v>1516</v>
       </c>
       <c r="F31" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Прилукская улица, 21-23А</t>
+          <t>Санкт-Петербург, Политехническая улица, 6</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Обводный Канал ~9 мин. пешком</t>
+          <t>Площадь Мужества ~12 мин. пешком</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2559,11 +2543,11 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500;2500</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -2573,44 +2557,44 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>725023</t>
+          <t>2085567</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Двухместный с 2 отдельными кроватями студия двухместная с одной совместной или раздельными кроватями</t>
+          <t>Просторная студия с креслом</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2475</v>
+        <v>3061</v>
       </c>
       <c r="D32" t="n">
         <v>9.6</v>
       </c>
       <c r="E32" t="n">
-        <v>41</v>
+        <v>430</v>
       </c>
       <c r="F32" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Захарьевская улица, 21</t>
+          <t>Санкт-Петербург, Энергетиков проспект, 8к2</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Чернышевская ~6 мин. пешком</t>
+          <t>Ладожская ~13 мин. пешком</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2623,15 +2607,15 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>2475</v>
+        <v>0</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -2641,44 +2625,44 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1986647</t>
+          <t>1012567</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Шикарная дизайнерская студия</t>
+          <t>Улучшенные апартаменты</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2057</v>
+        <v>5250</v>
       </c>
       <c r="D33" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="E33" t="n">
-        <v>24</v>
+        <v>427</v>
       </c>
       <c r="F33" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="G33" t="n">
         <v>2</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Витебский проспект, 99к1</t>
+          <t>Санкт-Петербург, Садовая улица, 28-30к1</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Купчино ~4 мин. пешком</t>
+          <t>Сенная площадь ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2687,19 +2671,19 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>110000000011111111000000110000000000000000000000000000000000</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>5813</v>
+        <v>0</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0;0;3429;3429;3429;4064;4572;4572;4318;0;0;0;0;0;0;0;0;0;4572;4572;4572;4572;4572;0;0;0;4572;4572;4572;5842;7112;8382;8382;7112;5842;5842;5842;5842;5842;5842;5842;5842;5842;5842;5842;5842;5842;6414;6985;6985;6985;6985;6985;6985;6985;6985;6985;6985;6985;6985</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -2709,44 +2693,44 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1957240</t>
+          <t>1105851</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Уютная студия в 5 минутах от аэропорта</t>
+          <t>Апартаменты студия комфорт</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1943</v>
+        <v>4950</v>
       </c>
       <c r="D34" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>21</v>
+        <v>484</v>
       </c>
       <c r="F34" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G34" t="n">
         <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Витебский проспект, 99к1</t>
+          <t>Санкт-Петербург, Лиговский проспект, 29</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Купчино ~4 мин. пешком</t>
+          <t>Площадь Восстания ~7 мин. пешком</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2759,7 +2743,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M34" t="n">
@@ -2767,7 +2751,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -2777,44 +2761,44 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1957286</t>
+          <t>1720449</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Видовая студия в ЖК Интуит</t>
+          <t>Апартамент стандартный с раздельными кроватями</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1943</v>
+        <v>2755</v>
       </c>
       <c r="D35" t="n">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>25</v>
+        <v>626</v>
       </c>
       <c r="F35" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G35" t="n">
         <v>2</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Витебский проспект, 101к1</t>
+          <t>Санкт-Петербург, реки Фонтанки набережная, 87</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Купчино ~3 мин. пешком</t>
+          <t>Сенная площадь ~7 мин. пешком</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2823,19 +2807,19 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>110110110000000000000000000000000000000000000000000000000000</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>5404</v>
+        <v>0</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0;0;0;0;0;0;0;0;4191;3683;3937;3937;3937;3937;3937;3937;3937;3937;4318;4318;4318;4318;4318;4318;4318;4318;4318;4318;4318;5842;7112;8382;8382;7112;5842;5842;5842;5842;5842;5842;5842;5842;5842;5842;5842;5842;5842;6096;6350;6350;6350;6350;6350;6350;6350;6350;6350;6350;6350;0</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -2845,44 +2829,44 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2161386</t>
+          <t>908275</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Уютная студия в апарт-комплексе Vertical We I Московская</t>
+          <t>Двухместный номер с 1 кроватью квартира-студия в Елагин-апарт</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2420</v>
+        <v>2783</v>
       </c>
       <c r="D36" t="n">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="E36" t="n">
-        <v>422</v>
+        <v>809</v>
       </c>
       <c r="F36" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G36" t="n">
         <v>2</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Орджоникидзе улица, 44А</t>
+          <t>Санкт-Петербург, Савушкина улица, 104</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Московская ~24 мин. пешком</t>
+          <t>Старая Деревня ~13 мин. пешком</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2899,11 +2883,11 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>4808</v>
+        <v>0</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2420;2420;2420;2662;2662;4235;4235;4235;3630;3267;3267;3872;4477;4477;3267;3267;3872;3872;3872;4477;4477;3267;3267;3872;3872;3872;4477;4477;3267;4840;5445;7260;7260;7260;7260;4840;4840;5445;5445;5445;7260;7260;4840;4840;5445;5445;5445;6050;6050;4840;4840;5445;7260;7260;7260;7260;4840;4840;5445;5445</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -2913,44 +2897,44 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-05-03 08:18</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>935949</t>
+          <t>1209575</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Апартаменты уютный</t>
+          <t>Апартаменты стандарт мансарда</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2375</v>
+        <v>9594</v>
       </c>
       <c r="D37" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>370</v>
+        <v>540</v>
       </c>
       <c r="F37" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G37" t="n">
         <v>2</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, 11-я Васильевского острова линия, 18В</t>
+          <t>Санкт-Петербург, Гривцова переулок, 4к2</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Василеостровская ~11 мин. пешком</t>
+          <t>Садовая ~7 мин. пешком</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2963,15 +2947,15 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>2375</v>
+        <v>0</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -2981,44 +2965,44 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-05-03 08:18</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2086576</t>
+          <t>1320319</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Двухместный номер с 1 кроватью Классический номер на Рубинштейна</t>
+          <t>Апартаменты атмосферная студия с балконом</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2420</v>
+        <v>5649</v>
       </c>
       <c r="D38" t="n">
         <v>9.5</v>
       </c>
       <c r="E38" t="n">
-        <v>233</v>
+        <v>2231</v>
       </c>
       <c r="F38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Рубинштейна улица, 30</t>
+          <t>Санкт-Петербург, Гривцова переулок, 24</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Достоевская ~1 мин. пешком</t>
+          <t>Садовая ~2 мин. пешком</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3035,11 +3019,11 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>5379</v>
+        <v>0</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2420;2420;2553;2553;2723;5324;5324;4840;4356;4356;4356;4356;4840;4840;4235;4235;4356;4356;4356;4961;4961;4235;4235;4356;4356;4356;5324;5324;4598;5445;6050;7502;7502;7502;7502;5445;5445;6050;0;6413;7502;7502;5445;5445;6050;6050;6050;7502;7502;5445;5445;6050;7502;7502;7502;7502;5445;5445;6050;6050</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -3049,29 +3033,29 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-05-03 08:18</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>937649</t>
+          <t>1926856</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Двухместный номер с 1 кроватью стандарт</t>
+          <t>Уютная студия</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1900</v>
+        <v>4176</v>
       </c>
       <c r="D39" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>1769</v>
+        <v>198</v>
       </c>
       <c r="F39" t="n">
         <v>15</v>
@@ -3081,12 +3065,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Садовая улица, 28-30к2</t>
+          <t>Санкт-Петербург, Гороховая улица, 30</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Гостиный двор ~7 мин. пешком</t>
+          <t>Сенная площадь ~5 мин. пешком</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3099,15 +3083,15 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -3117,44 +3101,44 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-05-03 08:18</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2046531</t>
+          <t>930277</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Мансарда эконом</t>
+          <t>Апартаменты атмосферная студия у Невского проспекта</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1901</v>
+        <v>5113</v>
       </c>
       <c r="D40" t="n">
         <v>9.6</v>
       </c>
       <c r="E40" t="n">
-        <v>620</v>
+        <v>522</v>
       </c>
       <c r="F40" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Коломенская улица, 14</t>
+          <t>Санкт-Петербург, Некрасова улица, 14литБс1</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Лиговский проспект ~7 мин. пешком</t>
+          <t>Маяковская ~11 мин. пешком</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3171,11 +3155,11 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>2248</v>
+        <v>0</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1901;1901;1901;1901;1901;1901;2201;1901;1901;1901;1901;1901;1901;1901;1901;1901;1901;1901;1901;3101;0;2701;2701;2701;2701;2701;2701;2701;2701;2701;2701;2701;2701;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -3185,44 +3169,44 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1728294</t>
+          <t>1471297</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Новая студия в ЖК In2it</t>
+          <t>Современная студия в апарт-комплексе YE'S Marata</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1943</v>
+        <v>3630</v>
       </c>
       <c r="D41" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="E41" t="n">
-        <v>31</v>
+        <v>174</v>
       </c>
       <c r="F41" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G41" t="n">
         <v>2</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Витебский проспект, 99к1</t>
+          <t>Санкт-Петербург, Социалистическая улица, 21</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Купчино ~4 мин. пешком</t>
+          <t>Обводный Канал ~11 мин. пешком</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3235,7 +3219,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M41" t="n">
@@ -3243,7 +3227,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -3253,44 +3237,44 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1904081</t>
+          <t>1346599</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Апартаменты студия возле московского вокзала + смарт тв</t>
+          <t>Апартаменты студия с видом на город</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2243</v>
+        <v>4711</v>
       </c>
       <c r="D42" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="E42" t="n">
-        <v>219</v>
+        <v>2228</v>
       </c>
       <c r="F42" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Гончарная улица, 11А</t>
+          <t>Санкт-Петербург, Гривцова переулок, 24</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~4 мин. пешком</t>
+          <t>Садовая ~2 мин. пешком</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3307,11 +3291,11 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>6251</v>
+        <v>0</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0;0;0;0;2220;4737;0;3737;3857;3421;4181;4181;4181;0;4181;4181;4181;0;0;0;0;4181;4181;0;4181;4181;4181;0;4599;6300;5727;5727;5727;5727;5727;5727;5727;5727;12144;12144;12144;12144;12144;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -3321,44 +3305,44 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>803069</t>
+          <t>921257</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Комфортная студия рядом с метро Площадь Мужества</t>
+          <t>Двухместный номер с 1 кроватью стандарт с 1 двуспальной кроватью</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2380</v>
+        <v>4950</v>
       </c>
       <c r="D43" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="E43" t="n">
-        <v>1516</v>
+        <v>427</v>
       </c>
       <c r="F43" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G43" t="n">
         <v>2</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Политехническая улица, 6</t>
+          <t>Санкт-Петербург, Садовая улица, 28-30к1</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Площадь Мужества ~12 мин. пешком</t>
+          <t>Сенная площадь ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3371,15 +3355,15 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>4180</v>
+        <v>0</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -3389,44 +3373,44 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2015794</t>
+          <t>2087072</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Номер с двуспальной кроватью</t>
+          <t>Двухуровневая студия в центре Петербурга</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2100</v>
+        <v>2602</v>
       </c>
       <c r="D44" t="n">
         <v>9.1</v>
       </c>
       <c r="E44" t="n">
-        <v>312</v>
+        <v>112</v>
       </c>
       <c r="F44" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Невский проспект, 136В</t>
+          <t>Санкт-Петербург, Боровая улица, 26-28</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~10 мин. пешком</t>
+          <t>Лиговский проспект ~10 мин. пешком</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3443,11 +3427,11 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>4307</v>
+        <v>0</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2100;2100;2300;2300;2200;2500;3500;2900;1600;1700;1800;2000;2300;3200;2300;2300;2300;2300;2500;3000;3500;2500;2900;2900;2900;2900;3000;4600;4000;4000;4600;4600;4600;5200;6300;4600;4600;5800;5800;5800;9200;9200;5800;5800;5800;5800;5800;6900;8100;5200;5200;5800;5800;5800;5800;6900;5800;5800;5800;5800</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -3457,44 +3441,44 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1901577</t>
+          <t>1702953</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Двухместный с 1 кроватью атмосферная комната</t>
+          <t>Двухместный с 1 кроватью обновленный апартамент с видом на Невский проспект</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2416</v>
+        <v>3640</v>
       </c>
       <c r="D45" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>121</v>
+        <v>476</v>
       </c>
       <c r="F45" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G45" t="n">
         <v>2</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, реки Фонтанки набережная, 101</t>
+          <t>Санкт-Петербург, Невский проспект, 91</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Сенная площадь ~7 мин. пешком</t>
+          <t>Площадь Восстания ~3 мин. пешком</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3507,15 +3491,15 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>2416</v>
+        <v>0</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2416</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -3525,44 +3509,44 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1533075</t>
+          <t>1070883</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Двухместный номер с 2 отдельными кроватями эконом с видом на город</t>
+          <t>Апартаменты стандарт с 1 двуспальной кроватью</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1400</v>
+        <v>4800</v>
       </c>
       <c r="D46" t="n">
-        <v>9.1</v>
+        <v>9.6</v>
       </c>
       <c r="E46" t="n">
-        <v>217</v>
+        <v>336</v>
       </c>
       <c r="F46" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G46" t="n">
         <v>2</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Рубинштейна улица, 32</t>
+          <t>Санкт-Петербург, Суворовский проспект, 65</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Достоевская ~2 мин. пешком</t>
+          <t>Чернышевская ~32 мин. пешком</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3571,19 +3555,19 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>38.3</v>
+        <v>0</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>111111100000011111111111011000000000000111000000000000000000</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>2355</v>
+        <v>0</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>0;0;0;0;0;0;0;1502;0;1700;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;2355;2410;2432;2411;2472;2366;2333;2333;0;0;0;0;0;0;0;2444;2444;2444;2444;2444;2444;2444;2444;2444;2444;2440;2440;2440;2440;0;0;0;0</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -3593,44 +3577,44 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1552905</t>
+          <t>784713</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Апартаменты в центре города у метро Площадь Восстания</t>
+          <t>Апартаменты улучшенная студия с кроватью king size и балконом</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1986</v>
+        <v>3110</v>
       </c>
       <c r="D47" t="n">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>294</v>
+        <v>329</v>
       </c>
       <c r="F47" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G47" t="n">
         <v>2</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, 8-я Советская улица, 10</t>
+          <t>Санкт-Петербург, Пулковское шоссе, 14с6</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Маяковская ~19 мин. пешком</t>
+          <t>Звёздная ~17 мин. пешком</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3647,11 +3631,11 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>4746</v>
+        <v>0</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1986;2138;2185;2185;2375;3135;4370;4370;3040;2660;2660;2660;4275;4465;3705;3705;3895;3895;3895;4465;4655;3791;3791;4076;4076;4076;4741;4940;4465;4465;6926;7401;7401;7781;7781;4465;4465;4655;4655;7401;7781;7781;5026;5026;5216;5216;5216;5691;5786;5216;5216;5406;5406;5406;5881;6166;5216;5216;5406;5406</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -3661,44 +3645,44 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1637686</t>
+          <t>1471401</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Апартаменты стандарт</t>
+          <t>Двухместный номер с 1 кроватью дизайн студия</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2100</v>
+        <v>3751</v>
       </c>
       <c r="D48" t="n">
-        <v>9.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="E48" t="n">
-        <v>237</v>
+        <v>809</v>
       </c>
       <c r="F48" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="G48" t="n">
         <v>2</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Столярный переулок, 9</t>
+          <t>Санкт-Петербург, Савушкина улица, 104</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Садовая ~6 мин. пешком</t>
+          <t>Старая Деревня ~13 мин. пешком</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3711,7 +3695,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M48" t="n">
@@ -3719,7 +3703,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
@@ -3729,44 +3713,44 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1784360</t>
+          <t>1562440</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Standard Loft на Лиговском</t>
+          <t>2-местная евро студия</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1700</v>
+        <v>4912</v>
       </c>
       <c r="D49" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="E49" t="n">
-        <v>521</v>
+        <v>280</v>
       </c>
       <c r="F49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G49" t="n">
         <v>2</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Пушкинская улица, 12</t>
+          <t>Санкт-Петербург, Звенигородская улица, 6</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~5 мин. пешком</t>
+          <t>Звенигородская ~2 мин. пешком</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3783,11 +3767,11 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>3358</v>
+        <v>0</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>1700;2300;1700;1800;1850;0;0;0;1900;1900;1900;2700;0;0;1800;2100;2100;2350;2550;2600;2550;2500;2500;2500;2500;2500;2500;2700;3400;3850;3850;3900;3950;3950;3900;3700;3700;3700;3750;3950;7700;4500;4300;3700;4050;4400;4400;4400;4400;4400;4400;4400;4400;4400;4400;4050;3700;3850;3850;3900</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
@@ -3797,44 +3781,44 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>945839</t>
+          <t>1970296</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Двухместный с 1 кроватью стандарт</t>
+          <t>студия возле московского вокзала + смарт тв</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2401</v>
+        <v>2220</v>
       </c>
       <c r="D50" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="E50" t="n">
-        <v>620</v>
+        <v>123</v>
       </c>
       <c r="F50" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G50" t="n">
         <v>2</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Коломенская улица, 14</t>
+          <t>Санкт-Петербург, Гончарная улица, 10</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Лиговский проспект ~7 мин. пешком</t>
+          <t>Площадь Восстания ~9 мин. пешком</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3847,15 +3831,15 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>2401</v>
+        <v>0</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
@@ -3865,44 +3849,44 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>945957</t>
+          <t>1775758</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Двухместный номер с 1 кроватью стандарт</t>
+          <t>Апартаменты с кухней</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2375</v>
+        <v>8249</v>
       </c>
       <c r="D51" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="E51" t="n">
-        <v>125</v>
+        <v>409</v>
       </c>
       <c r="F51" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Невский проспект, 102</t>
+          <t>Санкт-Петербург, Лиговский проспект, 44</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Маяковская ~2 мин. пешком</t>
+          <t>Площадь Восстания ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3919,11 +3903,11 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>7027</v>
+        <v>0</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2375;2660;3800;2850;2850;5225;6650;4750;3800;3800;5700;4750;6650;6175;5700;5700;5700;6650;6650;6650;6175;5700;5700;5700;5700;7600;6650;6175;5700;8360;8360;8930;8360;10355;10830;8835;8360;8360;8360;9025;0;9405;8835;8360;8360;8360;8360;8360;8835;8835;8360;8360;8360;8360;8360;8835;8835;8360;8360;8360</t>
+          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
@@ -3933,7 +3917,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-05-03 08:19</t>
+          <t>2026-05-03 16:37</t>
         </is>
       </c>
     </row>

--- a/data/sutochno_report.xlsx
+++ b/data/sutochno_report.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Объявления" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Объявления'!$A$1:$P$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Объявления'!$A$1:$P$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P63"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -540,37 +540,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>709383</t>
+          <t>760745</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Апартаменты двухуровневый стандарт трехместный</t>
+          <t>Апартаменты двухуровневая студия для двоих у Восстания</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5040</v>
+        <v>3960</v>
       </c>
       <c r="D2" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>585</v>
+        <v>514</v>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Владимирский проспект, 16</t>
+          <t>Санкт-Петербург, Лиговский проспект, 75</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Владимирская ~3 мин. пешком</t>
+          <t>Лиговский проспект ~7 мин. пешком</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
@@ -653,44 +653,44 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1209575</t>
+          <t>1346585</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Апартаменты стандарт мансарда</t>
+          <t>Студия в стиле Лофт</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6716</v>
+        <v>4902</v>
       </c>
       <c r="D4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="E4" t="n">
-        <v>540</v>
+        <v>1530</v>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Гривцова переулок, 4к2</t>
+          <t>Санкт-Петербург, Гривцова переулок, 24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Садовая ~7 мин. пешком</t>
+          <t>Садовая ~2 мин. пешком</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -713,44 +713,44 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1498426</t>
+          <t>2087207</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Атмосферная двухкомнатная квартира в центре</t>
+          <t>Уютная двухуровневая студия в центре Петербурга</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6108</v>
+        <v>2057</v>
       </c>
       <c r="D5" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>1530</v>
+        <v>300</v>
       </c>
       <c r="F5" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Гривцова переулок, 24</t>
+          <t>Санкт-Петербург, Курляндская улица, 6-8</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Садовая ~2 мин. пешком</t>
+          <t>Балтийская ~13 мин. пешком</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
@@ -789,13 +789,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2239</v>
+        <v>2118</v>
       </c>
       <c r="D6" t="n">
         <v>9.5</v>
       </c>
       <c r="E6" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F6" t="n">
         <v>24</v>
@@ -821,19 +821,11 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>000000000000000000000000000000000000000000000000000000000000</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>4185</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2239;2239;2239;2662;3388;3993;3388;2662;2904;2904;2904;3146;3146;2541;2541;2904;2904;2904;3146;3146;2541;2541;2904;3194;3194;3461;3461;3461;0;0;0;0;0;0;0;0;0;0;0;0;0;4235;4538;4840;4840;6958;9075;6655;4235;4538;6958;9075;9075;9075;6655;4235;4538;4840;4840;4840</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -841,44 +833,44 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-04 07:59</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>930277</t>
+          <t>581825</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Апартаменты атмосферная студия у Невского проспекта</t>
+          <t>Апартаменты двухуровневая студия стандарт</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4601</v>
+        <v>3750</v>
       </c>
       <c r="D7" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="E7" t="n">
-        <v>522</v>
+        <v>298</v>
       </c>
       <c r="F7" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
         <v>3</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Некрасова улица, 14литБс1</t>
+          <t>Санкт-Петербург, Лиговский проспект, 65</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Маяковская ~11 мин. пешком</t>
+          <t>Площадь Восстания ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -889,19 +881,11 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>000000000000000000000000000000000000000000000000000000000000</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>9258</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>4601;5113;4510;4711;0;0;7056;5381;5582;7525;5582;7592;7592;6989;6989;7592;7391;7391;7592;7391;6989;7190;7190;7190;6989;10440;10440;9636;9636;13388;13388;13388;13388;10708;9904;9904;10172;10172;12986;12986;14192;10440;10172;10440;10440;10440;10976;10976;10172;9904;10172;10172;10172;12986;13388;9904;9636;9904;9904;9904</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -909,44 +893,44 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-04 07:59</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>581825</t>
+          <t>1702953</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Апартаменты двухуровневая студия стандарт</t>
+          <t>Двухместный с 1 кроватью обновленный апартамент с видом на Невский проспект</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3750</v>
+        <v>3951</v>
       </c>
       <c r="D8" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>298</v>
+        <v>477</v>
       </c>
       <c r="F8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Лиговский проспект, 65</t>
+          <t>Санкт-Петербург, Невский проспект, 91</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~6 мин. пешком</t>
+          <t>Площадь Восстания ~3 мин. пешком</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -969,44 +953,44 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1346599</t>
+          <t>921257</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Апартаменты студия с видом на город</t>
+          <t>Двухместный номер с 1 кроватью стандарт с 1 двуспальной кроватью</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3998</v>
+        <v>5250</v>
       </c>
       <c r="D9" t="n">
         <v>9.5</v>
       </c>
       <c r="E9" t="n">
-        <v>2231</v>
+        <v>427</v>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Гривцова переулок, 24</t>
+          <t>Санкт-Петербург, Садовая улица, 28-30к1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Садовая ~2 мин. пешком</t>
+          <t>Сенная площадь ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1017,19 +1001,11 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>000000000000000000000000000000000000000000000000000000000000</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>8418</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>3998;4845;4577;4711;5716;7726;7458;5046;5046;5046;4778;6721;6721;6520;6520;6520;6520;6721;6922;6721;6520;6319;6520;6520;6520;9703;9502;8698;8698;12048;12048;12048;12048;9770;8966;8966;9234;9234;11914;12316;12718;9167;9167;9502;9502;9502;10038;10038;9502;9502;9502;9502;9234;12316;12718;9167;9234;9435;9435;9502</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1037,44 +1013,44 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-04 07:59</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1942433</t>
+          <t>1713953</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Классическая студия в апарт-комплексе WELL на Балтийской</t>
+          <t>Двухместные апартаменты с раздельными кроватями и мини-кухней</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3267</v>
+        <v>3480</v>
       </c>
       <c r="D10" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="E10" t="n">
-        <v>426</v>
+        <v>977</v>
       </c>
       <c r="F10" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Измайловский бульвар, 1к2</t>
+          <t>Санкт-Петербург, Невский проспект, 90-92</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Балтийская ~8 мин. пешком</t>
+          <t>Маяковская ~3 мин. пешком</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1097,29 +1073,29 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1713953</t>
+          <t>1070883</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Двухместные апартаменты с раздельными кроватями и мини-кухней</t>
+          <t>Апартаменты стандарт с 1 двуспальной кроватью</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3480</v>
+        <v>3360</v>
       </c>
       <c r="D11" t="n">
         <v>9.6</v>
       </c>
       <c r="E11" t="n">
-        <v>977</v>
+        <v>336</v>
       </c>
       <c r="F11" t="n">
         <v>17</v>
@@ -1129,12 +1105,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Невский проспект, 90-92</t>
+          <t>Санкт-Петербург, Суворовский проспект, 65</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Маяковская ~3 мин. пешком</t>
+          <t>Чернышевская ~32 мин. пешком</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1157,44 +1133,44 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1666187</t>
+          <t>806761</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Компактная студия New Horizon А5 для двоих у метро Сенная</t>
+          <t>Современная студия в 10 минутах пешком от метро пл. Мужества</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3879</v>
+        <v>3585</v>
       </c>
       <c r="D12" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>425</v>
+        <v>1516</v>
       </c>
       <c r="F12" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Апраксин переулок, 5</t>
+          <t>Санкт-Петербург, Политехническая улица, 6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Сенная площадь ~6 мин. пешком</t>
+          <t>Площадь Мужества ~12 мин. пешком</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1217,44 +1193,44 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1070883</t>
+          <t>1562440</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Апартаменты стандарт с 1 двуспальной кроватью</t>
+          <t>2-местная евро студия</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3360</v>
+        <v>4179</v>
       </c>
       <c r="D13" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="E13" t="n">
-        <v>336</v>
+        <v>280</v>
       </c>
       <c r="F13" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Суворовский проспект, 65</t>
+          <t>Санкт-Петербург, Звенигородская улица, 6</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Чернышевская ~32 мин. пешком</t>
+          <t>Звенигородская ~2 мин. пешком</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1277,44 +1253,44 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>806761</t>
+          <t>1970296</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Современная студия в 10 минутах пешком от метро пл. Мужества</t>
+          <t>студия возле московского вокзала + смарт тв</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3585</v>
+        <v>1998</v>
       </c>
       <c r="D14" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>1516</v>
+        <v>123</v>
       </c>
       <c r="F14" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Политехническая улица, 6</t>
+          <t>Санкт-Петербург, Гончарная улица, 10</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Площадь Мужества ~12 мин. пешком</t>
+          <t>Площадь Восстания ~9 мин. пешком</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1337,29 +1313,29 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1562440</t>
+          <t>1105851</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2-местная евро студия</t>
+          <t>Апартаменты студия комфорт</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4179</v>
+        <v>6039</v>
       </c>
       <c r="D15" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>280</v>
+        <v>485</v>
       </c>
       <c r="F15" t="n">
         <v>20</v>
@@ -1369,12 +1345,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Звенигородская улица, 6</t>
+          <t>Санкт-Петербург, Лиговский проспект, 29</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Звенигородская ~2 мин. пешком</t>
+          <t>Площадь Восстания ~7 мин. пешком</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1397,44 +1373,44 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1012567</t>
+          <t>731147</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Улучшенные апартаменты</t>
+          <t>Апартаменты стандарт</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4440</v>
+        <v>4410</v>
       </c>
       <c r="D16" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>427</v>
+        <v>119</v>
       </c>
       <c r="F16" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Садовая улица, 28-30к1</t>
+          <t>Санкт-Петербург, Лиговский проспект, 84/2Б</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Сенная площадь ~6 мин. пешком</t>
+          <t>Лиговский проспект ~1 мин. пешком</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1457,44 +1433,44 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1105851</t>
+          <t>1713984</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Апартаменты студия комфорт</t>
+          <t>Улучшенные апартаменты с одной кроватью и мини-кухней</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6710</v>
+        <v>3770</v>
       </c>
       <c r="D17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="E17" t="n">
-        <v>485</v>
+        <v>977</v>
       </c>
       <c r="F17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Лиговский проспект, 29</t>
+          <t>Санкт-Петербург, Невский проспект, 90</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~7 мин. пешком</t>
+          <t>Маяковская ~3 мин. пешком</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1517,23 +1493,23 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1720449</t>
+          <t>1720400</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Апартамент стандартный с раздельными кроватями</t>
+          <t>Апартамент эконом с раздельными кроватями</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2755</v>
+        <v>2349</v>
       </c>
       <c r="D18" t="n">
         <v>9.300000000000001</v>
@@ -1542,7 +1518,7 @@
         <v>626</v>
       </c>
       <c r="F18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G18" t="n">
         <v>2</v>
@@ -1571,11 +1547,11 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>7056</v>
+        <v>6681</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2755;2755;2755;2755;5800;5800;5800;2755;2755;4495;7250;7830;7830;6670;6670;6670;6670;6670;7250;7250;6670;6670;6670;7540;7540;0;0;0;0;8196;8954;8954;8449;7944;7438;7438;7438;8196;9298;9642;8678;7026;7975;7576;7576;8265;8954;7714;9092;7576;7576;7646;8334;8954;8334;7646;7576;7646;7714;0</t>
+          <t>2349;2320;2320;5220;5220;4785;2610;2320;3915;6090;6670;7250;6090;6090;6090;6090;6090;6670;6670;6090;6090;6090;7540;7540;0;0;0;0;7576;8265;8265;7806;7347;6888;6888;6888;7576;8610;9642;8678;7026;7975;7576;7576;8265;8265;7714;9092;7576;7576;7026;7714;8954;7714;7026;6888;7026;7163;0;0</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -1585,44 +1561,44 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-05-04 07:59</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>760745</t>
+          <t>709383</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Апартаменты двухуровневая студия для двоих у Восстания</t>
+          <t>Апартаменты двухуровневый стандарт трехместный</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3960</v>
+        <v>5040</v>
       </c>
       <c r="D19" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>514</v>
+        <v>585</v>
       </c>
       <c r="F19" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Лиговский проспект, 75</t>
+          <t>Санкт-Петербург, Владимирский проспект, 16</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Лиговский проспект ~7 мин. пешком</t>
+          <t>Владимирская ~3 мин. пешком</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1645,7 +1621,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
@@ -1705,32 +1681,32 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1346585</t>
+          <t>1320319</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Студия в стиле Лофт</t>
+          <t>Апартаменты атмосферная студия с балконом</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4902</v>
+        <v>5264</v>
       </c>
       <c r="D21" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="E21" t="n">
-        <v>1530</v>
+        <v>2233</v>
       </c>
       <c r="F21" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G21" t="n">
         <v>3</v>
@@ -1765,44 +1741,44 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1942400</t>
+          <t>1209575</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Студия с диваном в апарт-комплексе well на Балтийской</t>
+          <t>Апартаменты стандарт мансарда</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2420</v>
+        <v>6716</v>
       </c>
       <c r="D22" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>426</v>
+        <v>540</v>
       </c>
       <c r="F22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G22" t="n">
         <v>2</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Измайловский бульвар, 1к2</t>
+          <t>Санкт-Петербург, Гривцова переулок, 4к2</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Балтийская ~8 мин. пешком</t>
+          <t>Садовая ~7 мин. пешком</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1825,44 +1801,44 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>935949</t>
+          <t>880365</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Апартаменты уютный</t>
+          <t>Дизайнерский апартамент категории studio</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2850</v>
+        <v>4200</v>
       </c>
       <c r="D23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>370</v>
+        <v>139</v>
       </c>
       <c r="F23" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G23" t="n">
         <v>2</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, 11-я Васильевского острова линия, 18В</t>
+          <t>Санкт-Петербург, Заозёрная улица, 3к3</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Василеостровская ~11 мин. пешком</t>
+          <t>Фрунзенская ~9 мин. пешком</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1873,19 +1849,11 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>000000000000000000000000000000000000000000000000000000000000</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
-        <v>5973</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2850;2850;2850;0;0;0;2850;2850;2850;3800;3800;5225;5225;4750;4750;4750;4750;4750;5225;5225;4750;4750;4750;4750;4750;5225;5225;4750;6650;6650;8075;8075;8075;8075;6650;6460;6650;6650;6650;0;0;10450;8550;6650;8550;8550;7125;7125;6650;6650;6650;8550;6650;8075;8075;6650;6650;6650;6650;6650</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1893,44 +1861,44 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-05-04 07:59</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1389133</t>
+          <t>1328239</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Уютные двухместные апартаменты в жк зум</t>
+          <t>Семейная студия</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3027</v>
+        <v>4842</v>
       </c>
       <c r="D24" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="E24" t="n">
-        <v>347</v>
+        <v>2233</v>
       </c>
       <c r="F24" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Матроса Железняка улица, 2</t>
+          <t>Санкт-Петербург, Гривцова переулок, 24</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Чёрная речка ~13 мин. пешком</t>
+          <t>Садовая ~2 мин. пешком</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1953,44 +1921,44 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1328239</t>
+          <t>784633</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Семейная студия</t>
+          <t>Апартаменты стандартная студия с кроватью King size</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4842</v>
+        <v>2760</v>
       </c>
       <c r="D25" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>2233</v>
+        <v>329</v>
       </c>
       <c r="F25" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Гривцова переулок, 24</t>
+          <t>Санкт-Петербург, Пулковское шоссе, 14с6</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Садовая ~2 мин. пешком</t>
+          <t>Звёздная ~17 мин. пешком</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2013,44 +1981,44 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>784633</t>
+          <t>1942541</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Апартаменты стандартная студия с кроватью King size</t>
+          <t>Уютная трехместная студия БомбФлат на Фонтанке</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2650</v>
+        <v>4118</v>
       </c>
       <c r="D26" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="E26" t="n">
-        <v>329</v>
+        <v>75</v>
       </c>
       <c r="F26" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Пулковское шоссе, 14с6</t>
+          <t>Санкт-Петербург, реки Фонтанки набережная, 94</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Звёздная ~17 мин. пешком</t>
+          <t>Пушкинская ~7 мин. пешком</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2073,44 +2041,44 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1942541</t>
+          <t>1803466</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Уютная трехместная студия БомбФлат на Фонтанке</t>
+          <t>1-комнатная квартира</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4118</v>
+        <v>3599</v>
       </c>
       <c r="D27" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="F27" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, реки Фонтанки набережная, 94</t>
+          <t>Санкт-Петербург, Московский проспект, 224</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Пушкинская ~7 мин. пешком</t>
+          <t>Московская ~8 мин. пешком</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2133,44 +2101,44 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1702953</t>
+          <t>944615</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Двухместный с 1 кроватью обновленный апартамент с видом на Невский проспект</t>
+          <t>Студия у Московского вокзала</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3951</v>
+        <v>3213</v>
       </c>
       <c r="D28" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="E28" t="n">
-        <v>477</v>
+        <v>111</v>
       </c>
       <c r="F28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G28" t="n">
         <v>2</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Невский проспект, 91</t>
+          <t>Санкт-Петербург, Черняховского улица, 46</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~3 мин. пешком</t>
+          <t>Лиговский проспект ~3 мин. пешком</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2193,44 +2161,44 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>578163</t>
+          <t>1904075</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Апартаменты студия</t>
+          <t>Апартаменты студия возле московского вокзала + смарт тв</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2499</v>
+        <v>1998</v>
       </c>
       <c r="D29" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="E29" t="n">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="F29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G29" t="n">
         <v>2</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Полтавская улица, 5/29Б</t>
+          <t>Санкт-Петербург, Гончарная улица, 17</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~10 мин. пешком</t>
+          <t>Площадь Восстания ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2241,19 +2209,11 @@
       <c r="K29" t="n">
         <v>0</v>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>000000000000000000000000000000000000000000000000000000000000</t>
-        </is>
-      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
-        <v>5438</v>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>3230;3999;3999;3999;4335;0;2799;2799;2799;4199;4335;4999;4999;0;0;5299;4799;5599;3999;5599;3999;3999;5599;5599;5599;5599;5599;3999;4799;4799;6999;6999;6999;7999;5599;5599;5599;5599;5599;7999;7999;5799;5599;5599;5599;5599;5599;6999;6999;5599;6999;0;6999;7599;7599;5599;5599;5599;5399;5399</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2261,44 +2221,44 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-05-04 07:59</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>944615</t>
+          <t>1904863</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Студия у Московского вокзала</t>
+          <t>Апартаменты стандарт</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3213</v>
+        <v>3120</v>
       </c>
       <c r="D30" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="E30" t="n">
-        <v>111</v>
+        <v>851</v>
       </c>
       <c r="F30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G30" t="n">
         <v>2</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Черняховского улица, 46</t>
+          <t>Санкт-Петербург, Сердобольская улица, 7</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Лиговский проспект ~3 мин. пешком</t>
+          <t>Чёрная речка ~20 мин. пешком</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2321,44 +2281,44 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1471401</t>
+          <t>1471473</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Двухместный номер с 1 кроватью дизайн студия</t>
+          <t>Студия в апарт-комплексе Best Western Zoom</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3328</v>
+        <v>2541</v>
       </c>
       <c r="D31" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>809</v>
+        <v>61</v>
       </c>
       <c r="F31" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Савушкина улица, 104</t>
+          <t>Санкт-Петербург, Матроса Железняка улица, 2</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Старая Деревня ~13 мин. пешком</t>
+          <t>Чёрная речка ~13 мин. пешком</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2381,44 +2341,44 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1904863</t>
+          <t>788541</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Апартаменты стандарт</t>
+          <t>Апартаменты студио</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3000</v>
+        <v>4320</v>
       </c>
       <c r="D32" t="n">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>851</v>
+        <v>631</v>
       </c>
       <c r="F32" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G32" t="n">
         <v>2</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Сердобольская улица, 7</t>
+          <t>Санкт-Петербург, Гончарная улица, 8</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Чёрная речка ~20 мин. пешком</t>
+          <t>Площадь Восстания ~4 мин. пешком</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2441,44 +2401,44 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1970296</t>
+          <t>1957263</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>студия возле московского вокзала + смарт тв</t>
+          <t>Шикарная студия в стиле Boho</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1998</v>
+        <v>2515</v>
       </c>
       <c r="D33" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="E33" t="n">
-        <v>123</v>
+        <v>57</v>
       </c>
       <c r="F33" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G33" t="n">
         <v>2</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Гончарная улица, 10</t>
+          <t>Санкт-Петербург, Витебский улица, 99к1</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~9 мин. пешком</t>
+          <t>Купчино ~4 мин. пешком</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2501,44 +2461,44 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1775758</t>
+          <t>2004494</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Апартаменты с кухней</t>
+          <t>Студия с диваном в апарт-комплексе YE'S Marata</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7649</v>
+        <v>3025</v>
       </c>
       <c r="D34" t="n">
         <v>9.4</v>
       </c>
       <c r="E34" t="n">
-        <v>411</v>
+        <v>177</v>
       </c>
       <c r="F34" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Лиговский проспект, 44</t>
+          <t>Санкт-Петербург, Социалистическая улица, 21</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~6 мин. пешком</t>
+          <t>Обводный Канал ~11 мин. пешком</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2561,44 +2521,44 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1957263</t>
+          <t>1942606</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Шикарная студия в стиле Boho</t>
+          <t>Апартаменты современная двухместная студия</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2515</v>
+        <v>3998</v>
       </c>
       <c r="D35" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="E35" t="n">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F35" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G35" t="n">
         <v>2</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Витебский улица, 99к1</t>
+          <t>Санкт-Петербург, реки Фонтанки набережная, 94</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Купчино ~4 мин. пешком</t>
+          <t>Пушкинская ~7 мин. пешком</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2621,44 +2581,44 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>977025</t>
+          <t>1993982</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Атмосферная студия 5 в историческом центре</t>
+          <t>Апартаменты студия</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4239</v>
+        <v>2500</v>
       </c>
       <c r="D36" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="E36" t="n">
-        <v>1059</v>
+        <v>264</v>
       </c>
       <c r="F36" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G36" t="n">
         <v>2</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Можайская улица, 28</t>
+          <t>Санкт-Петербург, Политехническая улица, 6соор1</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Пушкинская ~10 мин. пешком</t>
+          <t>Площадь Мужества ~11 мин. пешком</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2669,19 +2629,11 @@
       <c r="K36" t="n">
         <v>0</v>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>000000000000000000000000000000000000000000000000000000000000</t>
-        </is>
-      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
-        <v>8096</v>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>4239;0;4644;4778;6252;7324;7324;5113;5113;5113;4912;6319;6319;5917;6118;6319;6520;6520;6721;6721;6319;6319;6520;6520;6520;9569;9904;8564;8564;11244;11244;11244;11244;9368;8564;8564;8832;8832;11244;11244;11244;8564;8564;8832;9100;9100;9636;9636;8832;8564;8832;8832;8832;11244;11244;8564;8564;8832;8832;9100</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2689,44 +2641,44 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-05-04 07:59</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2087207</t>
+          <t>933305</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Уютная двухуровневая студия в центре Петербурга</t>
+          <t>Апартаменты светлая студия</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2057</v>
+        <v>4540</v>
       </c>
       <c r="D37" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="E37" t="n">
-        <v>300</v>
+        <v>2233</v>
       </c>
       <c r="F37" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Курляндская улица, 6-8</t>
+          <t>Санкт-Петербург, Гривцова переулок, 24</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Балтийская ~13 мин. пешком</t>
+          <t>Садовая ~2 мин. пешком</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2749,35 +2701,35 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1320319</t>
+          <t>1498426</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Апартаменты атмосферная студия с балконом</t>
+          <t>Атмосферная двухкомнатная квартира в центре</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5264</v>
+        <v>6108</v>
       </c>
       <c r="D38" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="E38" t="n">
-        <v>2233</v>
+        <v>1530</v>
       </c>
       <c r="F38" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="G38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2809,29 +2761,29 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1926856</t>
+          <t>1942400</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Уютная студия</t>
+          <t>Студия с диваном в апарт-комплексе well на Балтийской</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3818</v>
+        <v>2420</v>
       </c>
       <c r="D39" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>198</v>
+        <v>426</v>
       </c>
       <c r="F39" t="n">
         <v>15</v>
@@ -2841,12 +2793,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Гороховая улица, 30</t>
+          <t>Санкт-Петербург, Измайловский бульвар, 1к2</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Сенная площадь ~5 мин. пешком</t>
+          <t>Балтийская ~8 мин. пешком</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2857,19 +2809,11 @@
       <c r="K39" t="n">
         <v>0</v>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>000000000000000000000000000000000000000000000000000000000000</t>
-        </is>
-      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
-        <v>8654</v>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>3818;5448;5448;5448;6252;8664;6588;5516;4913;5114;5315;7560;7560;7158;6957;6957;6756;6890;7225;7426;7091;7091;7292;7292;7158;9905;9905;9101;8900;12920;12920;12920;12920;9704;8900;8900;9168;9168;12920;12920;12920;9168;9168;9436;9436;9168;9704;9704;8900;8900;9168;9168;9168;12920;12920;8900;8900;9168;9168;9168</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2877,44 +2821,44 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-05-04 07:59</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>880365</t>
+          <t>1389133</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Дизайнерский апартамент категории studio</t>
+          <t>Уютные двухместные апартаменты в жк зум</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4200</v>
+        <v>2964</v>
       </c>
       <c r="D40" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="E40" t="n">
-        <v>139</v>
+        <v>347</v>
       </c>
       <c r="F40" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G40" t="n">
         <v>2</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Заозёрная улица, 3к3</t>
+          <t>Санкт-Петербург, Матроса Железняка улица, 2</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Фрунзенская ~9 мин. пешком</t>
+          <t>Чёрная речка ~13 мин. пешком</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2937,44 +2881,44 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1471297</t>
+          <t>1425651</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Современная студия в апарт-комплексе YE'S Marata</t>
+          <t>Апартаменты двухуровневые стандарт</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3630</v>
+        <v>7949</v>
       </c>
       <c r="D41" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F41" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Социалистическая улица, 21</t>
+          <t>Санкт-Петербург, Жуковского улица, 7-9</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Обводный Канал ~11 мин. пешком</t>
+          <t>Маяковская ~9 мин. пешком</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2985,19 +2929,11 @@
       <c r="K41" t="n">
         <v>0</v>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>000000000000000000000000000000000000000000000000000000000000</t>
-        </is>
-      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
-        <v>8226</v>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>3630;3267;4598;4598;7260;8470;7260;6050;5687;5687;5687;7260;6655;6050;6050;6655;6655;6655;6655;6655;6050;6050;6655;6655;6655;6655;6655;6050;8470;9680;12100;12100;12100;10285;8470;8470;9680;9680;9680;12100;10285;8470;8470;9680;9680;9680;12100;10285;8470;8470;9680;12100;12100;11495;10890;8470;8470;9680;9680;9680</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -3005,44 +2941,44 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-05-04 07:59</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1425651</t>
+          <t>1666187</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Апартаменты двухуровневые стандарт</t>
+          <t>Компактная студия New Horizon А5 для двоих у метро Сенная</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7949</v>
+        <v>3879</v>
       </c>
       <c r="D42" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="E42" t="n">
-        <v>173</v>
+        <v>425</v>
       </c>
       <c r="F42" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Жуковского улица, 7-9</t>
+          <t>Санкт-Петербург, Апраксин переулок, 5</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Маяковская ~9 мин. пешком</t>
+          <t>Сенная площадь ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3065,44 +3001,44 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>921257</t>
+          <t>2087072</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Двухместный номер с 1 кроватью стандарт с 1 двуспальной кроватью</t>
+          <t>Двухуровневая студия в центре Петербурга</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5250</v>
+        <v>2239</v>
       </c>
       <c r="D43" t="n">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="E43" t="n">
-        <v>427</v>
+        <v>112</v>
       </c>
       <c r="F43" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Садовая улица, 28-30к1</t>
+          <t>Санкт-Петербург, Боровая улица, 26-28</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Сенная площадь ~6 мин. пешком</t>
+          <t>Лиговский проспект ~10 мин. пешком</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3125,44 +3061,44 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2087072</t>
+          <t>521465</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Двухуровневая студия в центре Петербурга</t>
+          <t>Студия</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2602</v>
+        <v>2699</v>
       </c>
       <c r="D44" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="E44" t="n">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="F44" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G44" t="n">
         <v>3</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Боровая улица, 26-28</t>
+          <t>Санкт-Петербург, Полтавская улица, 5</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Лиговский проспект ~10 мин. пешком</t>
+          <t>Площадь Восстания ~7 мин. пешком</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3173,19 +3109,11 @@
       <c r="K44" t="n">
         <v>0</v>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>000000000000000000000000000000000000000000000000000000000000</t>
-        </is>
-      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
-        <v>4213</v>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>2602;2602;2602;2602;4598;4840;4598;4598;4235;4235;4235;4840;4840;3630;3630;4235;4235;4235;4840;4840;3630;3630;4235;4235;4235;6050;6050;4840;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -3193,44 +3121,44 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-05-04 07:59</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>521465</t>
+          <t>784713</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Студия</t>
+          <t>Апартаменты улучшенная студия с кроватью king size и балконом</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2699</v>
+        <v>2990</v>
       </c>
       <c r="D45" t="n">
-        <v>8.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>173</v>
+        <v>329</v>
       </c>
       <c r="F45" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Полтавская улица, 5</t>
+          <t>Санкт-Петербург, Пулковское шоссе, 14с6</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~7 мин. пешком</t>
+          <t>Звёздная ~17 мин. пешком</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3253,44 +3181,44 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>784713</t>
+          <t>2085567</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Апартаменты улучшенная студия с кроватью king size и балконом</t>
+          <t>Просторная студия с креслом</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2880</v>
+        <v>2577</v>
       </c>
       <c r="D46" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="E46" t="n">
-        <v>329</v>
+        <v>433</v>
       </c>
       <c r="F46" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Пулковское шоссе, 14с6</t>
+          <t>Санкт-Петербург, Энергетиков проспект, 8к2</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Звёздная ~17 мин. пешком</t>
+          <t>Ладожская ~13 мин. пешком</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3313,44 +3241,44 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1904075</t>
+          <t>1012567</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Апартаменты студия возле московского вокзала + смарт тв</t>
+          <t>Улучшенные апартаменты</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1998</v>
+        <v>4440</v>
       </c>
       <c r="D47" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="E47" t="n">
-        <v>245</v>
+        <v>427</v>
       </c>
       <c r="F47" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G47" t="n">
         <v>2</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Гончарная улица, 17</t>
+          <t>Санкт-Петербург, Садовая улица, 28-30к1</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~6 мин. пешком</t>
+          <t>Сенная площадь ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3373,44 +3301,44 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1562447</t>
+          <t>1775758</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Шикарная студия</t>
+          <t>Апартаменты с кухней</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4510</v>
+        <v>7649</v>
       </c>
       <c r="D48" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="E48" t="n">
-        <v>77</v>
+        <v>411</v>
       </c>
       <c r="F48" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G48" t="n">
         <v>3</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Реки Фонтанки набережная, 110</t>
+          <t>Санкт-Петербург, Лиговский проспект, 44</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Технологический институт-2 ~8 мин. пешком</t>
+          <t>Площадь Восстания ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3419,21 +3347,13 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>000000000100000000000000000000000000000000000000000000000000</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
-        <v>8998</v>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>4239;4711;4711;4711;6185;7525;7525;4711;0;0;5448;7458;7458;7056;7056;7257;7257;7257;7458;7458;7056;7056;7257;7257;7257;10306;10306;9770;9770;12316;12316;12316;12316;10306;9770;9770;10038;10038;12316;12316;12316;9770;9770;10038;10038;10038;10306;10306;9770;9770;10038;10038;10038;12316;12316;9770;9770;10038;10038;10038</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -3441,44 +3361,44 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-05-04 07:59</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1728294</t>
+          <t>1926972</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Новая студия в ЖК In2it</t>
+          <t>Светлая студия в центре</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2743</v>
+        <v>4721</v>
       </c>
       <c r="D49" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>31</v>
+        <v>199</v>
       </c>
       <c r="F49" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Витебский проспект, 99к1</t>
+          <t>Санкт-Петербург, Гороховая улица, 30</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Купчино ~4 мин. пешком</t>
+          <t>Сенная площадь ~5 мин. пешком</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3487,21 +3407,13 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>000000000001000000000001000000000000000000000000000000000000</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
-        <v>5189</v>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>2629;3048;3048;3048;3810;4318;4318;4064;3429;3683;0;0;3683;3683;3683;3683;3683;4191;4191;4191;4191;4191;0;0;4191;4191;4191;4191;5715;6985;8255;8255;6985;5715;5715;5715;5715;5715;5715;5715;5715;5715;5715;5715;5715;5715;6032;6350;6350;6350;6350;6350;6350;6350;6350;6350;6350;6350;6350;6350</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -3509,44 +3421,44 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-05-04 07:59</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1471473</t>
+          <t>1464729</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Студия в апарт-комплексе Best Western Zoom</t>
+          <t>Апартаменты стандарт</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2844</v>
+        <v>2236</v>
       </c>
       <c r="D50" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="E50" t="n">
-        <v>61</v>
+        <v>216</v>
       </c>
       <c r="F50" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G50" t="n">
         <v>2</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Матроса Железняка улица, 2</t>
+          <t>Санкт-Петербург, Марата улица, 56-58/29</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Чёрная речка ~13 мин. пешком</t>
+          <t>Лиговский проспект ~5 мин. пешком</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3569,44 +3481,44 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>788541</t>
+          <t>803069</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Апартаменты студио</t>
+          <t>Комфортная студия рядом с метро Площадь Мужества</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4320</v>
+        <v>3347</v>
       </c>
       <c r="D51" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>631</v>
+        <v>1516</v>
       </c>
       <c r="F51" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G51" t="n">
         <v>2</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Гончарная улица, 8</t>
+          <t>Санкт-Петербург, Политехническая улица, 6</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~4 мин. пешком</t>
+          <t>Площадь Мужества ~12 мин. пешком</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3629,740 +3541,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-05-05 08:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>933305</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Апартаменты светлая студия</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>4540</v>
-      </c>
-      <c r="D52" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="E52" t="n">
-        <v>2233</v>
-      </c>
-      <c r="F52" t="n">
-        <v>23</v>
-      </c>
-      <c r="G52" t="n">
-        <v>3</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, Гривцова переулок, 24</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Садовая ~2 мин. пешком</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>Открыть</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>2026-05-05 08:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>1803466</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>1-комнатная квартира</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>3599</v>
-      </c>
-      <c r="D53" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="E53" t="n">
-        <v>105</v>
-      </c>
-      <c r="F53" t="n">
-        <v>32</v>
-      </c>
-      <c r="G53" t="n">
-        <v>4</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, Московский проспект, 224</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Московская ~8 мин. пешком</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>Открыть</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>2026-05-05 08:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2004494</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Студия с диваном в апарт-комплексе YE'S Marata</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>3267</v>
-      </c>
-      <c r="D54" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="E54" t="n">
-        <v>177</v>
-      </c>
-      <c r="F54" t="n">
-        <v>19</v>
-      </c>
-      <c r="G54" t="n">
-        <v>2</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, Социалистическая улица, 21</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Обводный Канал ~11 мин. пешком</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>Открыть</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>2026-05-05 08:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>1942606</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Апартаменты современная двухместная студия</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>3998</v>
-      </c>
-      <c r="D55" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="E55" t="n">
-        <v>75</v>
-      </c>
-      <c r="F55" t="n">
-        <v>16</v>
-      </c>
-      <c r="G55" t="n">
-        <v>2</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, реки Фонтанки набережная, 94</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Пушкинская ~7 мин. пешком</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>Открыть</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>2026-05-05 08:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>1464729</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Апартаменты стандарт</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>2236</v>
-      </c>
-      <c r="D56" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="E56" t="n">
-        <v>216</v>
-      </c>
-      <c r="F56" t="n">
-        <v>14</v>
-      </c>
-      <c r="G56" t="n">
-        <v>2</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, Марата улица, 56-58/29</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Лиговский проспект ~5 мин. пешком</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>Открыть</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>2026-05-05 08:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>803069</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Комфортная студия рядом с метро Площадь Мужества</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>3347</v>
-      </c>
-      <c r="D57" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="E57" t="n">
-        <v>1516</v>
-      </c>
-      <c r="F57" t="n">
-        <v>18</v>
-      </c>
-      <c r="G57" t="n">
-        <v>2</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, Политехническая улица, 6</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Площадь Мужества ~12 мин. пешком</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" s="2" t="inlineStr">
-        <is>
-          <t>Открыть</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>2026-05-05 08:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2162631</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Уютная студия</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>2783</v>
-      </c>
-      <c r="D58" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="E58" t="n">
-        <v>57</v>
-      </c>
-      <c r="F58" t="n">
-        <v>17</v>
-      </c>
-      <c r="G58" t="n">
-        <v>2</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, Приморский проспект, 6</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Чёрная речка ~22 мин. пешком</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>000000000000000000000000000000000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="M58" t="n">
-        <v>4709</v>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>2541;2541;2420;2420;2420;2420;3630;3630;3630;3630;4235;4235;4235;4235;5203;5203;5203;5445;5445;4840;4840;5203;5203;5203;5445;5445;4840;6050;6050;6050;6050;6655;6655;5445;5445;6050;6050;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
-        </is>
-      </c>
-      <c r="O58" s="2" t="inlineStr">
-        <is>
-          <t>Открыть</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>2026-05-05 08:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>1993982</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Апартаменты студия</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>2250</v>
-      </c>
-      <c r="D59" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="E59" t="n">
-        <v>264</v>
-      </c>
-      <c r="F59" t="n">
-        <v>23</v>
-      </c>
-      <c r="G59" t="n">
-        <v>2</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, Политехническая улица, 6соор1</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Площадь Мужества ~11 мин. пешком</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" s="2" t="inlineStr">
-        <is>
-          <t>Открыть</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>2026-05-05 08:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2085567</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Просторная студия с креслом</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>2819</v>
-      </c>
-      <c r="D60" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="E60" t="n">
-        <v>433</v>
-      </c>
-      <c r="F60" t="n">
-        <v>27</v>
-      </c>
-      <c r="G60" t="n">
-        <v>3</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, Энергетиков проспект, 8к2</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Ладожская ~13 мин. пешком</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" s="2" t="inlineStr">
-        <is>
-          <t>Открыть</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>2026-05-05 08:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>1926972</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Светлая студия в центре</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>4721</v>
-      </c>
-      <c r="D61" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="E61" t="n">
-        <v>199</v>
-      </c>
-      <c r="F61" t="n">
-        <v>20</v>
-      </c>
-      <c r="G61" t="n">
-        <v>3</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, Гороховая улица, 30</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Сенная площадь ~5 мин. пешком</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" s="2" t="inlineStr">
-        <is>
-          <t>Открыть</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>2026-05-05 08:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>1713984</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Улучшенные апартаменты с одной кроватью и мини-кухней</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>3770</v>
-      </c>
-      <c r="D62" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="E62" t="n">
-        <v>977</v>
-      </c>
-      <c r="F62" t="n">
-        <v>18</v>
-      </c>
-      <c r="G62" t="n">
-        <v>2</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, Невский проспект, 90</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Маяковская ~3 мин. пешком</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" s="2" t="inlineStr">
-        <is>
-          <t>Открыть</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>2026-05-05 08:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>1720400</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Апартамент эконом с раздельными кроватями</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>2349</v>
-      </c>
-      <c r="D63" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="E63" t="n">
-        <v>626</v>
-      </c>
-      <c r="F63" t="n">
-        <v>13</v>
-      </c>
-      <c r="G63" t="n">
-        <v>2</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, реки Фонтанки набережная, 87</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Сенная площадь ~7 мин. пешком</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>Открыть</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>2026-05-05 08:20</t>
+          <t>2026-05-05 09:16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P63"/>
+  <autoFilter ref="A1:P51"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -4414,18 +3598,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId62"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/sutochno_report.xlsx
+++ b/data/sutochno_report.xlsx
@@ -581,11 +581,19 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>6177</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>3960;4400;4620;4620;5170;5170;4400;4400;4400;4400;4400;4400;0;4400;4400;4400;4400;4675;4950;4950;4950;4950;4950;4950;7150;7150;7150;7150;7150;7150;7150;7150;7150;7150;7150;7150;7150;7150;7645;7398;7150;7150;7150;7150;7150;7150;7150;7150;7150;7150;7150;7150;7150;7150;7150;7150;7150;7150;7150;7150</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -593,7 +601,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:27</t>
         </is>
       </c>
     </row>
@@ -615,7 +623,7 @@
         <v>9.5</v>
       </c>
       <c r="E3" t="n">
-        <v>3036</v>
+        <v>3037</v>
       </c>
       <c r="F3" t="n">
         <v>30</v>
@@ -641,11 +649,19 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
+        <v>7308</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3770;3770;3770;5720;5720;5720;5720;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;13000;13000;13000;13000;13000;13000;13000;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;6760;9100</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -653,32 +669,32 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:27</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1346585</t>
+          <t>1320319</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Студия в стиле Лофт</t>
+          <t>Апартаменты атмосферная студия с балконом</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4902</v>
+        <v>5264</v>
       </c>
       <c r="D4" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="E4" t="n">
-        <v>1530</v>
+        <v>2233</v>
       </c>
       <c r="F4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
@@ -701,11 +717,19 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
+        <v>8796</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>5265;5649;5649;5716;7726;6788;5850;5850;5850;5850;7659;7659;7458;7458;7458;7458;7659;7860;7659;7458;7257;7458;7458;7458;9033;8832;8028;8028;13522;13522;13522;13522;9100;8296;8296;8564;8564;13388;13790;14192;8497;8899;8832;9234;9234;9368;9368;9234;9234;9234;8832;8564;13790;14192;8497;8564;8765;8765;8832;10038</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -713,44 +737,44 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:27</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2087207</t>
+          <t>1498426</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Уютная двухуровневая студия в центре Петербурга</t>
+          <t>Атмосферная двухкомнатная квартира в центре</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2057</v>
+        <v>6108</v>
       </c>
       <c r="D5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="E5" t="n">
-        <v>300</v>
+        <v>1531</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Курляндская улица, 6-8</t>
+          <t>Санкт-Петербург, Гривцова переулок, 24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Балтийская ~13 мин. пешком</t>
+          <t>Садовая ~2 мин. пешком</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -761,11 +785,19 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
+        <v>10041</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>6109;6587;5247;6252;8128;7860;6788;6788;6788;6788;8597;8597;8396;8396;8396;8396;8597;7458;7257;8396;8195;7056;7056;7056;11445;11244;10440;10440;14996;14996;14996;14996;11512;10708;10708;9636;9636;12718;15264;15666;10909;10909;9904;11244;9904;11780;10440;9904;9904;9904;9904;10976;15264;15666;10909;10976;11177;11177;11244;11780</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -773,44 +805,44 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>955145</t>
+          <t>880365</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Студия в апарт-комплексе "Салют" на Звездной</t>
+          <t>Дизайнерский апартамент категории studio</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2118</v>
+        <v>4200</v>
       </c>
       <c r="D6" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>309</v>
+        <v>141</v>
       </c>
       <c r="F6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Пулковское шоссе, 14с6</t>
+          <t>Санкт-Петербург, Заозёрная улица, 3к3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Звёздная ~17 мин. пешком</t>
+          <t>Фрунзенская ~9 мин. пешком</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -821,11 +853,19 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
+        <v>5665</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>4200;4200;4200;5400;6000;4800;4200;4200;4200;4200;4800;4800;4200;4200;4200;4200;4200;4800;4800;4200;4200;4200;4200;4200;4800;4800;4200;5400;8100;8400;8400;7800;7200;6600;6000;6000;6000;7800;7800;7800;6600;6000;6000;6000;6000;6600;6600;6000;6000;6000;6000;6000;7200;7800;6000;6000;6000;6000;6000;7200</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -833,44 +873,44 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>581825</t>
+          <t>1328239</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Апартаменты двухуровневая студия стандарт</t>
+          <t>Семейная студия</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3750</v>
+        <v>4842</v>
       </c>
       <c r="D7" t="n">
         <v>9.5</v>
       </c>
       <c r="E7" t="n">
-        <v>298</v>
+        <v>2233</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Лиговский проспект, 65</t>
+          <t>Санкт-Петербург, Гривцова переулок, 24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~6 мин. пешком</t>
+          <t>Садовая ~2 мин. пешком</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -881,11 +921,19 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr"/>
+        <v>9850</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4842;4845;5917;7056;7726;8798;6118;6118;6118;6118;7927;7927;7726;7726;7726;7726;7927;8128;7927;7726;7525;7726;7726;7726;11043;10842;10038;10038;14058;14058;14058;14058;11110;10306;10306;10574;10574;13924;14326;14728;10507;10507;10842;10842;10842;11378;11378;10842;10842;10842;10842;10574;14326;14728;10507;10574;10775;10775;10842;11378</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -893,44 +941,44 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1702953</t>
+          <t>784633</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Двухместный с 1 кроватью обновленный апартамент с видом на Невский проспект</t>
+          <t>Апартаменты стандартная студия с кроватью King size</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3951</v>
+        <v>2760</v>
       </c>
       <c r="D8" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>477</v>
+        <v>331</v>
       </c>
       <c r="F8" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Невский проспект, 91</t>
+          <t>Санкт-Петербург, Пулковское шоссе, 14с6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~3 мин. пешком</t>
+          <t>Звёздная ~17 мин. пешком</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -941,11 +989,19 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
+        <v>4471</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2760;2420;2420;3220;3455;3050;2760;2760;2760;3105;3450;3335;3220;3335;4025;4715;4945;5060;4830;4715;4830;4830;4830;4945;4830;4370;4315;6790;8181;8181;6870;5421;4490;4260;4375;4490;5180;5283;4800;4317;4260;4375;4490;4490;4605;4720;4490;4260;4375;4490;4490;4950;5410;4835;4260;4375;4490;4720;5065;5180</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -953,44 +1009,44 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>921257</t>
+          <t>1942541</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Двухместный номер с 1 кроватью стандарт с 1 двуспальной кроватью</t>
+          <t>Уютная трехместная студия БомбФлат на Фонтанке</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5250</v>
+        <v>4118</v>
       </c>
       <c r="D9" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="E9" t="n">
-        <v>427</v>
+        <v>75</v>
       </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Садовая улица, 28-30к1</t>
+          <t>Санкт-Петербург, реки Фонтанки набережная, 94</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Сенная площадь ~6 мин. пешком</t>
+          <t>Пушкинская ~7 мин. пешком</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1001,11 +1057,19 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
+        <v>8054</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4119;4376;4376;5515;6520;6520;4912;5113;5113;5113;6788;6788;6185;5984;6185;6386;6587;6788;6788;5984;5984;6386;6386;6386;9100;9100;8564;8564;11110;10708;10708;10708;9368;8564;8564;8832;8832;10708;10708;10708;8564;8832;9368;9636;9636;9904;9904;9100;9100;9100;9100;8832;11110;11110;8832;8832;9100;8832;8832;9368</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1013,44 +1077,44 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1713953</t>
+          <t>1803466</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Двухместные апартаменты с раздельными кроватями и мини-кухней</t>
+          <t>1-комнатная квартира</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3480</v>
+        <v>3599</v>
       </c>
       <c r="D10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>977</v>
+        <v>105</v>
       </c>
       <c r="F10" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Невский проспект, 90-92</t>
+          <t>Санкт-Петербург, Московский проспект, 224</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Маяковская ~3 мин. пешком</t>
+          <t>Московская ~8 мин. пешком</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1059,13 +1123,21 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+        <v>36.7</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>001111000001000000111000000000001111111110000000001111100000</t>
+        </is>
+      </c>
       <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr"/>
+        <v>5530</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>3599;0;0;0;0;0;4000;4000;0;4099;0;0;4299;4299;4299;4299;4599;0;0;0;0;4299;4299;4599;4999;4999;4599;6499;6499;6599;7499;0;0;0;0;0;0;0;0;0;0;6599;6599;6599;6599;6599;6599;6599;6599;0;0;0;0;0;0;6599;6599;6199;6199;6199</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1073,44 +1145,44 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1070883</t>
+          <t>944615</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Апартаменты стандарт с 1 двуспальной кроватью</t>
+          <t>Студия у Московского вокзала</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3360</v>
+        <v>3213</v>
       </c>
       <c r="D11" t="n">
         <v>9.6</v>
       </c>
       <c r="E11" t="n">
-        <v>336</v>
+        <v>111</v>
       </c>
       <c r="F11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Суворовский проспект, 65</t>
+          <t>Санкт-Петербург, Черняховского улица, 46</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Чернышевская ~32 мин. пешком</t>
+          <t>Лиговский проспект ~3 мин. пешком</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1121,11 +1193,19 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr"/>
+        <v>6485</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>3213;4590;4104;6930;6930;6930;2970;3618;3618;3618;6264;6264;4104;4104;4104;4104;4104;5292;5292;4860;4860;4860;4860;4860;6264;6264;3942;7308;7308;7308;6930;6930;6930;6930;6930;6930;6930;8820;9576;9576;7308;7308;9198;9198;9198;8820;8820;7308;7308;7308;8064;8064;9576;9576;8064;7308;7308;6552;6552;6930</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1133,44 +1213,44 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>806761</t>
+          <t>1904075</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Современная студия в 10 минутах пешком от метро пл. Мужества</t>
+          <t>Апартаменты студия возле московского вокзала + смарт тв</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3585</v>
+        <v>1998</v>
       </c>
       <c r="D12" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="E12" t="n">
-        <v>1516</v>
+        <v>246</v>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Политехническая улица, 6</t>
+          <t>Санкт-Петербург, Гончарная улица, 17</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Площадь Мужества ~12 мин. пешком</t>
+          <t>Площадь Восстания ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1181,11 +1261,19 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
+        <v>5764</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1998;2220;2220;4737;4737;3737;3857;3421;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4599;4599;5478;4980;4980;4980;4980;4980;4980;4980;4980;12144;12144;12144;12144;12144;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1193,44 +1281,44 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1562440</t>
+          <t>1904863</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2-местная евро студия</t>
+          <t>Апартаменты стандарт</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4179</v>
+        <v>3120</v>
       </c>
       <c r="D13" t="n">
         <v>9.5</v>
       </c>
       <c r="E13" t="n">
-        <v>280</v>
+        <v>853</v>
       </c>
       <c r="F13" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Звенигородская улица, 6</t>
+          <t>Санкт-Петербург, Сердобольская улица, 7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Звенигородская ~2 мин. пешком</t>
+          <t>Чёрная речка ~20 мин. пешком</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1241,11 +1329,19 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr"/>
+        <v>4843</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>3120;2820;2520;2640;3000;3000;2160;2340;2640;2940;3180;3000;2760;2760;2760;2760;3240;3720;3540;3360;3360;3360;3360;3540;3720;3480;3480;3720;4260;4800;6000;7200;6420;5640;5940;6240;6900;7560;7560;6660;6240;6240;6240;6240;6480;6720;6480;6240;6240;6240;6240;6900;7560;6900;6240;6240;6240;6240;6480;6720</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1253,7 +1349,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
@@ -1301,11 +1397,19 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr"/>
+        <v>5764</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1998;2220;2220;4737;4737;3737;3857;3421;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4181;4599;4599;5478;4980;4980;4980;4980;4980;4980;4980;4980;12144;12144;12144;12144;12144;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980;6980</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1313,44 +1417,44 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1105851</t>
+          <t>788541</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Апартаменты студия комфорт</t>
+          <t>Апартаменты студио</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6039</v>
+        <v>4320</v>
       </c>
       <c r="D15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>485</v>
+        <v>631</v>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Лиговский проспект, 29</t>
+          <t>Санкт-Петербург, Гончарная улица, 8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~7 мин. пешком</t>
+          <t>Площадь Восстания ~4 мин. пешком</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1361,11 +1465,19 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr"/>
+        <v>7768</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>4320;4320;4680;5760;7560;6840;4560;4680;4920;4920;5868;5988;5220;5220;5220;5220;5220;5868;5988;5220;5220;5220;5220;5220;6708;6828;6588;6588;10428;10788;10788;11628;11628;7788;7788;7788;7788;10788;11988;11988;8748;8748;8868;8868;8868;9948;10188;9348;9348;9348;9348;9348;10428;11148;9348;9348;9348;9348;9348;10428</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1373,44 +1485,44 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>731147</t>
+          <t>1720449</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Апартаменты стандарт</t>
+          <t>Апартамент стандартный с раздельными кроватями</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4410</v>
+        <v>2755</v>
       </c>
       <c r="D16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>119</v>
+        <v>627</v>
       </c>
       <c r="F16" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Лиговский проспект, 84/2Б</t>
+          <t>Санкт-Петербург, реки Фонтанки набережная, 87</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Лиговский проспект ~1 мин. пешком</t>
+          <t>Сенная площадь ~7 мин. пешком</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1421,11 +1533,19 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr"/>
+        <v>7081</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2755;2465;2465;5800;5800;5365;2755;2465;4495;6670;7250;7830;6670;6670;6670;6670;6670;7250;7250;6670;6670;6670;7540;7540;0;0;0;0;8196;8954;8954;8449;7944;7438;7438;7438;8196;9298;9642;8678;7026;7975;7576;7576;8265;8954;7714;9092;0;7576;7646;8334;8954;8334;7646;7576;7646;7714;0;0</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1433,44 +1553,44 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1713984</t>
+          <t>2004494</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Улучшенные апартаменты с одной кроватью и мини-кухней</t>
+          <t>Студия с диваном в апарт-комплексе YE'S Marata</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3770</v>
+        <v>3025</v>
       </c>
       <c r="D17" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="E17" t="n">
-        <v>977</v>
+        <v>177</v>
       </c>
       <c r="F17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Невский проспект, 90</t>
+          <t>Санкт-Петербург, Социалистическая улица, 21</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Маяковская ~3 мин. пешком</t>
+          <t>Обводный Канал ~11 мин. пешком</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1481,11 +1601,19 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="inlineStr"/>
+        <v>7024</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>3025;3025;3267;5445;6050;5445;4840;4477;4477;4477;5445;5445;4840;4840;5445;5445;5445;5445;5445;4840;4840;5445;5445;5445;5445;5445;4840;7260;8470;10285;10285;10285;8772;7260;7260;8470;8470;8470;10285;8772;7260;7260;8470;8470;8470;10285;8772;7260;7260;8470;10285;10285;9982;10890;7260;7260;8470;8470;8470;9680</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1493,44 +1621,44 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1720400</t>
+          <t>1942606</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Апартамент эконом с раздельными кроватями</t>
+          <t>Апартаменты современная двухместная студия</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2349</v>
+        <v>3998</v>
       </c>
       <c r="D18" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="E18" t="n">
-        <v>626</v>
+        <v>75</v>
       </c>
       <c r="F18" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G18" t="n">
         <v>2</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, реки Фонтанки набережная, 87</t>
+          <t>Санкт-Петербург, реки Фонтанки набережная, 94</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Сенная площадь ~7 мин. пешком</t>
+          <t>Пушкинская ~7 мин. пешком</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1547,11 +1675,11 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>6681</v>
+        <v>7748</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2349;2320;2320;5220;5220;4785;2610;2320;3915;6090;6670;7250;6090;6090;6090;6090;6090;6670;6670;6090;6090;6090;7540;7540;0;0;0;0;7576;8265;8265;7806;7347;6888;6888;6888;7576;8610;9642;8678;7026;7975;7576;7576;8265;8265;7714;9092;7576;7576;7026;7714;8954;7714;7026;6888;7026;7163;0;0</t>
+          <t>3998;4242;4242;5113;6118;6118;4778;4979;4979;4979;6654;6654;6051;5850;6051;6252;6453;6654;6654;5850;5850;6252;6386;6252;8698;8698;8162;8162;10708;10306;10306;10306;8966;8162;8162;8430;8430;10306;10306;10306;8162;8430;8966;9234;9234;9502;9502;8698;8698;8698;8698;8430;10708;10708;8430;8430;8698;8430;8430;8966</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -1561,7 +1689,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
@@ -1609,11 +1737,19 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="inlineStr"/>
+        <v>6412</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>5040;5040;5040;7280;7280;5645;5040;5040;5040;5040;5645;6648;5712;5040;5040;5712;5712;5824;5824;5040;5712;5712;5712;5712;5824;5824;5040;7280;7280;7280;7280;7672;7672;7280;7280;7280;7280;7280;9274;8285;6496;6496;6496;7168;7168;7280;6888;6496;7168;7168;6496;6496;0;7280;6496;6496;6496;6496;7168;0</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1621,44 +1757,44 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:27</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>908275</t>
+          <t>933305</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Двухместный номер с 1 кроватью квартира-студия в Елагин-апарт</t>
+          <t>Апартаменты светлая студия</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2783</v>
+        <v>4540</v>
       </c>
       <c r="D20" t="n">
-        <v>9.1</v>
+        <v>9.5</v>
       </c>
       <c r="E20" t="n">
-        <v>809</v>
+        <v>2233</v>
       </c>
       <c r="F20" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Савушкина улица, 104</t>
+          <t>Санкт-Петербург, Гривцова переулок, 24</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Старая Деревня ~13 мин. пешком</t>
+          <t>Садовая ~2 мин. пешком</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1669,11 +1805,19 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="inlineStr"/>
+        <v>8771</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>4541;4845;4845;5984;7994;7726;5046;5046;5046;5046;6855;6855;6654;6654;6654;6654;6855;7056;6855;6654;6453;6654;6654;6654;9971;9770;8966;8966;12584;12584;12584;12584;10038;9234;9234;9502;9502;12450;12852;13254;9435;9435;9770;9770;9770;10306;10306;9770;9770;9770;9770;9502;12852;13254;9435;9502;9703;9703;9770;10306</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1681,44 +1825,44 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:27</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1320319</t>
+          <t>2087207</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Апартаменты атмосферная студия с балконом</t>
+          <t>Уютная двухуровневая студия в центре Петербурга</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5264</v>
+        <v>2057</v>
       </c>
       <c r="D21" t="n">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>2233</v>
+        <v>300</v>
       </c>
       <c r="F21" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Гривцова переулок, 24</t>
+          <t>Санкт-Петербург, Курляндская улица, 6-8</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Садовая ~2 мин. пешком</t>
+          <t>Балтийская ~13 мин. пешком</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1727,13 +1871,21 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
+        <v>53.3</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000011111111111111111111111111111111</t>
+        </is>
+      </c>
       <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="inlineStr"/>
+        <v>3296</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2057;2057;2057;3207;3388;3207;2904;2783;2783;2783;3025;3025;2783;2783;3812;3812;3812;4417;4417;3207;3207;3812;3812;3812;4417;4417;3207;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1741,44 +1893,44 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:27</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1209575</t>
+          <t>1942400</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Апартаменты стандарт мансарда</t>
+          <t>Студия с диваном в апарт-комплексе well на Балтийской</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6716</v>
+        <v>2420</v>
       </c>
       <c r="D22" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>540</v>
+        <v>427</v>
       </c>
       <c r="F22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G22" t="n">
         <v>2</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Гривцова переулок, 4к2</t>
+          <t>Санкт-Петербург, Измайловский бульвар, 1к2</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Садовая ~7 мин. пешком</t>
+          <t>Балтийская ~8 мин. пешком</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1789,11 +1941,19 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="inlineStr"/>
+        <v>5643</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2420;2420;2420;4840;4840;4598;4477;4477;4477;4477;5445;5445;4235;4235;4840;4840;4840;5445;5445;4235;4235;4840;4840;4840;5808;5808;4840;5445;6050;7865;7865;7865;7865;5445;5445;5808;5808;6050;7865;7865;5445;5445;5808;5808;5808;7865;7865;5445;5445;5808;7865;7865;7865;7865;5445;5445;5808;6050;6050;6655</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1801,44 +1961,44 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:27</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>880365</t>
+          <t>1389133</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Дизайнерский апартамент категории studio</t>
+          <t>Уютные двухместные апартаменты в жк зум</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4200</v>
+        <v>2964</v>
       </c>
       <c r="D23" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="E23" t="n">
-        <v>139</v>
+        <v>348</v>
       </c>
       <c r="F23" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G23" t="n">
         <v>2</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Заозёрная улица, 3к3</t>
+          <t>Санкт-Петербург, Матроса Железняка улица, 2</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Фрунзенская ~9 мин. пешком</t>
+          <t>Чёрная речка ~13 мин. пешком</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1849,11 +2009,19 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="inlineStr"/>
+        <v>5138</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2964;3160;3160;4000;4000;4000;3720;3720;3720;3720;3860;3860;3860;3720;3720;3720;3720;4560;4560;4280;4280;4280;4280;4280;4560;4560;4280;5820;5820;5820;5820;6100;6100;5820;5820;5820;5820;5820;6100;6100;5820;5820;5820;5820;5820;6100;6100;5820;5820;5820;5820;5820;6100;6100;5820;5820;5820;8200;8200;8480</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1861,44 +2029,44 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:27</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1328239</t>
+          <t>1425651</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Семейная студия</t>
+          <t>Апартаменты двухуровневые стандарт</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4842</v>
+        <v>7949</v>
       </c>
       <c r="D24" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>2233</v>
+        <v>174</v>
       </c>
       <c r="F24" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Гривцова переулок, 24</t>
+          <t>Санкт-Петербург, Жуковского улица, 7-9</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Садовая ~2 мин. пешком</t>
+          <t>Маяковская ~9 мин. пешком</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1909,11 +2077,19 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="inlineStr"/>
+        <v>12762</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>7949;7949;5249;8249;13949;13949;7799;7499;7499;7499;7499;7499;7499;7499;10649;10799;10799;10799;0;10649;10649;10649;10649;10649;11249;11249;10649;13499;19949;19949;19949;19949;19949;12149;12149;12149;12149;17999;17999;17999;17999;13049;13049;13049;13049;13049;13049;13049;13049;13049;13049;13049;20099;20099;20099;12299;12299;15449;15449;0</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1921,44 +2097,44 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:27</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>784633</t>
+          <t>1666187</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Апартаменты стандартная студия с кроватью King size</t>
+          <t>Компактная студия New Horizon А5 для двоих у метро Сенная</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2760</v>
+        <v>3879</v>
       </c>
       <c r="D25" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="E25" t="n">
-        <v>329</v>
+        <v>425</v>
       </c>
       <c r="F25" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="G25" t="n">
         <v>2</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Пулковское шоссе, 14с6</t>
+          <t>Санкт-Петербург, Апраксин переулок, 5</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Звёздная ~17 мин. пешком</t>
+          <t>Сенная площадь ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1969,11 +2145,19 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="inlineStr"/>
+        <v>6786</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>3879;4310;4310;6060;6060;5500;4310;4500;4500;4310;7560;6810;6060;6060;6060;6060;6060;7750;7000;6250;6250;6250;6250;7000;7750;7000;6250;7000;7750;7750;8500;9250;7940;6630;6630;6630;7190;8500;9250;7940;6630;6630;6630;6630;7380;8130;7380;6630;0;7750;7750;8500;9250;7940;6630;6630;6630;6630;7380;8130</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -1981,44 +2165,44 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1942541</t>
+          <t>2087072</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Уютная трехместная студия БомбФлат на Фонтанке</t>
+          <t>Двухуровневая студия в центре Петербурга</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4118</v>
+        <v>2239</v>
       </c>
       <c r="D26" t="n">
-        <v>9.6</v>
+        <v>9.1</v>
       </c>
       <c r="E26" t="n">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="F26" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G26" t="n">
         <v>3</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, реки Фонтанки набережная, 94</t>
+          <t>Санкт-Петербург, Боровая улица, 26-28</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Пушкинская ~7 мин. пешком</t>
+          <t>Лиговский проспект ~10 мин. пешком</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2029,11 +2213,19 @@
       <c r="K26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="inlineStr"/>
+        <v>3816</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2239;2239;2239;3993;4235;3993;4235;3509;3509;3509;4114;4114;3267;3267;3872;3872;3872;4477;4477;3267;3267;3872;3872;3872;5687;5687;4477;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2041,44 +2233,44 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1803466</t>
+          <t>521465</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1-комнатная квартира</t>
+          <t>Студия</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3599</v>
+        <v>2699</v>
       </c>
       <c r="D27" t="n">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="E27" t="n">
-        <v>105</v>
+        <v>174</v>
       </c>
       <c r="F27" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Московский проспект, 224</t>
+          <t>Санкт-Петербург, Полтавская улица, 5</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Московская ~8 мин. пешком</t>
+          <t>Площадь Восстания ~7 мин. пешком</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2087,13 +2279,21 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>000001000011111000001110000000000000000111000111000000111111</t>
+        </is>
+      </c>
       <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="inlineStr"/>
+        <v>4950</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2700;2999;2999;3335;0;0;2999;2999;3199;0;0;0;0;0;0;3799;4599;4599;4599;0;0;0;0;4599;4599;4599;4599;5299;5299;5999;5999;5999;0;5999;5999;5999;5999;5999;0;0;0;0;5999;5999;0;0;0;0;5999;5999;5999;5999;6599;0;0;0;0;0;0;0</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2101,44 +2301,44 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>944615</t>
+          <t>784713</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Студия у Московского вокзала</t>
+          <t>Апартаменты улучшенная студия с кроватью king size и балконом</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3213</v>
+        <v>2990</v>
       </c>
       <c r="D28" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>111</v>
+        <v>331</v>
       </c>
       <c r="F28" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G28" t="n">
         <v>2</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Черняховского улица, 46</t>
+          <t>Санкт-Петербург, Пулковское шоссе, 14с6</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Лиговский проспект ~3 мин. пешком</t>
+          <t>Звёздная ~17 мин. пешком</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2149,11 +2349,19 @@
       <c r="K28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="inlineStr"/>
+        <v>4691</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2990;2650;2650;3450;3685;3280;2990;2990;2990;3335;3680;3565;3450;3565;4255;4945;5175;5290;5060;4945;5060;5060;5060;5175;5060;4600;4545;7075;8487;8487;7143;5661;4720;4490;4605;4720;5410;0;5007;4524;4490;4605;4720;4720;4835;4950;4720;4490;4605;4720;4720;5180;5640;5065;4490;4605;4720;4950;5295;5410</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2161,44 +2369,44 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1904075</t>
+          <t>2085567</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Апартаменты студия возле московского вокзала + смарт тв</t>
+          <t>Просторная студия с креслом</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1998</v>
+        <v>2577</v>
       </c>
       <c r="D29" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="E29" t="n">
-        <v>245</v>
+        <v>433</v>
       </c>
       <c r="F29" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Гончарная улица, 17</t>
+          <t>Санкт-Петербург, Энергетиков проспект, 8к2</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~6 мин. пешком</t>
+          <t>Ладожская ~13 мин. пешком</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2209,11 +2417,19 @@
       <c r="K29" t="n">
         <v>0</v>
       </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="inlineStr"/>
+        <v>5648</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2577;2420;2577;3872;4477;4477;3872;3872;4341;4341;4864;4864;4234;4234;4704;4704;4704;5227;5227;4234;4234;4704;4704;4704;5227;5227;4234;6050;6655;7260;7260;7260;7260;6050;6050;6655;6655;6655;7260;7260;6050;6050;6655;6655;6655;7260;7260;6050;6050;6655;7260;7260;7260;7260;6050;6050;6655;6655;6655;7260</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2221,44 +2437,44 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1904863</t>
+          <t>1012567</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Апартаменты стандарт</t>
+          <t>Улучшенные апартаменты</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3120</v>
+        <v>4440</v>
       </c>
       <c r="D30" t="n">
         <v>9.5</v>
       </c>
       <c r="E30" t="n">
-        <v>851</v>
+        <v>427</v>
       </c>
       <c r="F30" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G30" t="n">
         <v>2</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Сердобольская улица, 7</t>
+          <t>Санкт-Петербург, Садовая улица, 28-30к1</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Чёрная речка ~20 мин. пешком</t>
+          <t>Сенная площадь ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2269,11 +2485,19 @@
       <c r="K30" t="n">
         <v>0</v>
       </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="inlineStr"/>
+        <v>10314</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>4440;4800;4800;9750;10350;9750;6450;6000;6000;6900;10950;10950;8550;8550;7950;7950;7950;7950;7950;7950;7950;7950;7950;7950;8550;8550;7950;10350;10350;13800;13800;13800;13800;9750;10350;10350;10350;11550;17550;17550;15300;11550;11550;11550;13050;13800;13800;9750;10350;10350;13800;13800;14550;14550;9750;9750;9750;10950;10950;13800</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2281,7 +2505,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
@@ -2329,11 +2553,19 @@
       <c r="K31" t="n">
         <v>0</v>
       </c>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="inlineStr"/>
+        <v>5812</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2541;2844;2965;3630;3993;4235;3388;3388;3388;3388;5264;5445;4840;4840;4840;4840;4840;5445;5445;4840;4840;5445;5445;5445;6655;6655;5445;5748;7260;8470;8470;8470;6958;5445;5748;6050;6050;7260;8470;6958;5445;5748;6050;6050;7260;8470;6958;5445;5748;7260;8470;8470;8470;6958;5445;5748;6050;6050;6050;6897</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2341,44 +2573,44 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>788541</t>
+          <t>1926972</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Апартаменты студио</t>
+          <t>Светлая студия в центре</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4320</v>
+        <v>4721</v>
       </c>
       <c r="D32" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>631</v>
+        <v>199</v>
       </c>
       <c r="F32" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Гончарная улица, 8</t>
+          <t>Санкт-Петербург, Гороховая улица, 30</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~4 мин. пешком</t>
+          <t>Сенная площадь ~5 мин. пешком</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2389,11 +2621,19 @@
       <c r="K32" t="n">
         <v>0</v>
       </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="inlineStr"/>
+        <v>9144</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>4722;5046;5046;6051;8664;6588;5516;4913;5114;5315;8028;8028;7626;7425;7425;7224;7358;7693;7894;7091;7091;7292;7292;7158;9905;9905;9101;9636;13388;13388;13388;13388;10440;9636;9636;9904;9904;12920;12920;12920;9904;9904;10172;10172;9904;10440;10440;9636;9636;9904;9904;9904;13388;13388;9636;9636;9904;9904;9904;10976</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2401,44 +2641,44 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1957263</t>
+          <t>1464729</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Шикарная студия в стиле Boho</t>
+          <t>Апартаменты стандарт</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2515</v>
+        <v>2236</v>
       </c>
       <c r="D33" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="E33" t="n">
-        <v>57</v>
+        <v>216</v>
       </c>
       <c r="F33" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G33" t="n">
         <v>2</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Витебский улица, 99к1</t>
+          <t>Санкт-Петербург, Марата улица, 56-58/29</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Купчино ~4 мин. пешком</t>
+          <t>Лиговский проспект ~5 мин. пешком</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2449,11 +2689,19 @@
       <c r="K33" t="n">
         <v>0</v>
       </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="inlineStr"/>
+        <v>5706</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2236;2795;3105;3267;5832;5805;4050;4563;4563;4563;4901;4901;4563;5805;5805;5805;5805;6480;6480;5805;5805;5805;5805;5805;6480;6480;5805;5805;5805;5805;5805;6480;6480;5805;5805;5805;5805;5805;8424;8424;7547;5805;5805;5805;5805;6480;6480;5805;5805;5805;5805;5805;6480;6480;5805;5805;5805;5805;5805;6480</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2461,44 +2709,44 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2004494</t>
+          <t>803069</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Студия с диваном в апарт-комплексе YE'S Marata</t>
+          <t>Комфортная студия рядом с метро Площадь Мужества</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3025</v>
+        <v>3347</v>
       </c>
       <c r="D34" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>177</v>
+        <v>1517</v>
       </c>
       <c r="F34" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G34" t="n">
         <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Социалистическая улица, 21</t>
+          <t>Санкт-Петербург, Политехническая улица, 6</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Обводный Канал ~11 мин. пешком</t>
+          <t>Площадь Мужества ~12 мин. пешком</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2509,11 +2757,19 @@
       <c r="K34" t="n">
         <v>0</v>
       </c>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="inlineStr"/>
+        <v>6203</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>3347;3620;3620;4600;5720;4040;4040;4040;4040;4320;5160;5160;4880;4880;4880;4880;4880;5160;5160;4880;4880;4880;4880;4880;5160;5160;4880;6840;6840;6840;6840;8800;8800;6840;7100;6840;6840;6840;7540;7540;6840;6840;6840;6840;6840;8800;8800;6840;6840;6840;6840;6840;8800;8800;6840;6840;6840;8520;8520;10480</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2521,44 +2777,44 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1942606</t>
+          <t>2162631</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Апартаменты современная двухместная студия</t>
+          <t>Уютная студия</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3998</v>
+        <v>2541</v>
       </c>
       <c r="D35" t="n">
-        <v>9.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F35" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G35" t="n">
         <v>2</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, реки Фонтанки набережная, 94</t>
+          <t>Санкт-Петербург, Приморский проспект, 6</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Пушкинская ~7 мин. пешком</t>
+          <t>Чёрная речка ~22 мин. пешком</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2569,11 +2825,19 @@
       <c r="K35" t="n">
         <v>0</v>
       </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="inlineStr"/>
+        <v>4843</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2541;2541;2662;3993;3993;3993;3630;3630;3630;3630;4235;4235;4235;4235;5203;5203;5203;5445;5445;4840;4840;5203;5203;5203;5445;5445;4840;6050;6050;6050;6050;6655;6655;5445;5445;6050;6050;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2581,44 +2845,44 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1993982</t>
+          <t>908275</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Апартаменты студия</t>
+          <t>Двухместный номер с 1 кроватью квартира-студия в Елагин-апарт</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2500</v>
+        <v>2783</v>
       </c>
       <c r="D36" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="E36" t="n">
-        <v>264</v>
+        <v>809</v>
       </c>
       <c r="F36" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G36" t="n">
         <v>2</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Политехническая улица, 6соор1</t>
+          <t>Санкт-Петербург, Савушкина улица, 104</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Площадь Мужества ~11 мин. пешком</t>
+          <t>Старая Деревня ~13 мин. пешком</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2629,11 +2893,19 @@
       <c r="K36" t="n">
         <v>0</v>
       </c>
-      <c r="L36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="inlineStr"/>
+        <v>5585</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2783;2783;2783;4538;4538;4538;4114;4114;4235;4235;4840;4840;4175;4175;5022;5022;5022;7507;5962;4417;4417;5022;5022;5022;5627;5627;4417;5445;6050;8228;8228;8228;8228;5445;5445;6050;6050;6050;8228;8228;5445;5445;6050;6050;6050;6655;6655;5445;5445;6050;6050;6050;6655;6655;5445;5445;6050;6050;6050;6655</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2641,29 +2913,29 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:27</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>933305</t>
+          <t>1346585</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Апартаменты светлая студия</t>
+          <t>Студия в стиле Лофт</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4540</v>
+        <v>4902</v>
       </c>
       <c r="D37" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="E37" t="n">
-        <v>2233</v>
+        <v>1530</v>
       </c>
       <c r="F37" t="n">
         <v>23</v>
@@ -2689,11 +2961,19 @@
       <c r="K37" t="n">
         <v>0</v>
       </c>
-      <c r="L37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="inlineStr"/>
+        <v>9018</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>4903;5247;5247;6118;8128;7860;5448;5448;5448;5448;7257;7257;7056;7056;7056;7056;7257;7458;7257;7056;6855;7056;7056;7056;10105;9904;9100;9100;12852;12852;12852;12852;10172;9368;9368;9636;9636;12718;13120;13522;9569;9569;9904;9904;9904;10440;10440;9904;9904;9904;9904;9636;13120;13522;9569;9636;9837;9837;9904;10440</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2701,44 +2981,44 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:27</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1498426</t>
+          <t>1209575</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Атмосферная двухкомнатная квартира в центре</t>
+          <t>Апартаменты стандарт мансарда</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6108</v>
+        <v>6716</v>
       </c>
       <c r="D38" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>1530</v>
+        <v>545</v>
       </c>
       <c r="F38" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="G38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Гривцова переулок, 24</t>
+          <t>Санкт-Петербург, Гривцова переулок, 4к2</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Садовая ~2 мин. пешком</t>
+          <t>Садовая ~7 мин. пешком</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2749,11 +3029,19 @@
       <c r="K38" t="n">
         <v>0</v>
       </c>
-      <c r="L38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="inlineStr"/>
+        <v>12322</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>6716;9594;9594;10530;13869;12006;8901;8892;8892;9594;11355;11355;8016;9592;9592;9592;9592;11907;11907;10764;10764;10764;10764;10764;11907;11907;9570;10065;17775;16704;15921;15921;17019;11385;11385;11385;11385;15138;28350;20367;13248;12627;12627;12627;12627;14823;14823;12006;12006;12006;12006;12006;14355;14355;11385;12006;12006;12006;12006;16281</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2761,44 +3049,44 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:27</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1942400</t>
+          <t>955145</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Студия с диваном в апарт-комплексе well на Балтийской</t>
+          <t>Студия в апарт-комплексе "Салют" на Звездной</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2420</v>
+        <v>2118</v>
       </c>
       <c r="D39" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="E39" t="n">
-        <v>426</v>
+        <v>309</v>
       </c>
       <c r="F39" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G39" t="n">
         <v>2</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Измайловский бульвар, 1к2</t>
+          <t>Санкт-Петербург, Пулковское шоссе, 14с6</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Балтийская ~8 мин. пешком</t>
+          <t>Звёздная ~17 мин. пешком</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2809,11 +3097,19 @@
       <c r="K39" t="n">
         <v>0</v>
       </c>
-      <c r="L39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="inlineStr"/>
+        <v>4711</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2118;2118;2541;2783;3025;2783;2541;2541;2541;2541;3146;3146;2541;2541;2904;2904;2904;3146;3146;2541;2541;2904;3194;3194;3461;3461;3461;4538;6958;9075;9075;9075;6655;4235;4538;4840;4840;6958;9075;6655;4235;4538;4840;4840;6958;9075;6655;4235;4538;6958;9075;9075;9075;6655;4235;4538;4840;4840;4840;5445</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2821,44 +3117,44 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:27</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1389133</t>
+          <t>581825</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Уютные двухместные апартаменты в жк зум</t>
+          <t>Апартаменты двухуровневая студия стандарт</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2964</v>
+        <v>3750</v>
       </c>
       <c r="D40" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="E40" t="n">
-        <v>347</v>
+        <v>298</v>
       </c>
       <c r="F40" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Матроса Железняка улица, 2</t>
+          <t>Санкт-Петербург, Лиговский проспект, 65</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Чёрная речка ~13 мин. пешком</t>
+          <t>Площадь Восстания ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2869,11 +3165,19 @@
       <c r="K40" t="n">
         <v>0</v>
       </c>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="inlineStr"/>
+        <v>6347</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>3750;3750;3750;6125;6125;6125;4375;4375;4375;4375;4375;4250;4375;4375;4375;4375;4375;0;4375;4375;4375;4375;4375;4375;0;4375;4375;7906;7763;7763;7906;7763;7763;7906;7763;7906;7906;7906;0;0;7906;7906;7906;7906;7906;7906;7906;7906;7906;7906;7906;7906;7906;7906;7906;7906;7906;7906;7906;0</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2881,44 +3185,44 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:27</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1425651</t>
+          <t>1702953</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Апартаменты двухуровневые стандарт</t>
+          <t>Двухместный с 1 кроватью обновленный апартамент с видом на Невский проспект</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>7949</v>
+        <v>3951</v>
       </c>
       <c r="D41" t="n">
-        <v>9.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>173</v>
+        <v>477</v>
       </c>
       <c r="F41" t="n">
         <v>16</v>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Жуковского улица, 7-9</t>
+          <t>Санкт-Петербург, Невский проспект, 91</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Маяковская ~9 мин. пешком</t>
+          <t>Площадь Восстания ~3 мин. пешком</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2929,11 +3233,19 @@
       <c r="K41" t="n">
         <v>0</v>
       </c>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="inlineStr"/>
+        <v>7884</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>3951;4390;4390;7450;8200;6700;5140;5890;5890;5890;7390;7390;5890;6640;6640;6640;6640;9700;8950;8200;8200;8200;8200;8200;9700;8950;8200;8640;8982;9338;9130;8920;8355;7790;7999;8564;9130;9130;8920;8355;7790;7790;8146;8502;8502;8502;8355;8208;8417;8982;9338;9130;8920;8355;7790;7790;8146;8502;8502;8502</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -2941,39 +3253,39 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1666187</t>
+          <t>921257</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Компактная студия New Horizon А5 для двоих у метро Сенная</t>
+          <t>Двухместный номер с 1 кроватью стандарт с 1 двуспальной кроватью</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3879</v>
+        <v>4725</v>
       </c>
       <c r="D42" t="n">
         <v>9.5</v>
       </c>
       <c r="E42" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F42" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G42" t="n">
         <v>2</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Апраксин переулок, 5</t>
+          <t>Санкт-Петербург, Садовая улица, 28-30к1</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2989,11 +3301,19 @@
       <c r="K42" t="n">
         <v>0</v>
       </c>
-      <c r="L42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="inlineStr"/>
+        <v>9767</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>4725;4500;4500;9450;10050;9450;6150;5700;5700;6600;10650;10650;8250;8250;7650;7650;7650;7650;7650;7650;7650;7650;7650;7650;8250;8250;7650;10050;10050;13500;13500;13500;13500;9450;10050;10050;10050;11250;13800;12900;15000;11250;11250;11250;12750;13500;13500;9450;10050;10050;13500;13500;11400;9480;9450;9450;9450;10650;10650;13500</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -3001,44 +3321,44 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2087072</t>
+          <t>1713953</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Двухуровневая студия в центре Петербурга</t>
+          <t>Двухместные апартаменты с раздельными кроватями и мини-кухней</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2239</v>
+        <v>3480</v>
       </c>
       <c r="D43" t="n">
-        <v>9.1</v>
+        <v>9.6</v>
       </c>
       <c r="E43" t="n">
-        <v>112</v>
+        <v>977</v>
       </c>
       <c r="F43" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Боровая улица, 26-28</t>
+          <t>Санкт-Петербург, Невский проспект, 90-92</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Лиговский проспект ~10 мин. пешком</t>
+          <t>Маяковская ~3 мин. пешком</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3049,11 +3369,19 @@
       <c r="K43" t="n">
         <v>0</v>
       </c>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="inlineStr"/>
+        <v>8013</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>3480;3480;3480;5365;5365;4785;3480;3480;5220;5220;8410;8990;7830;7830;7830;7830;7830;8990;7830;8410;8410;8410;8410;7250;7540;8700;7830;8410;8410;11709;11709;10676;8816;7990;7990;8540;9092;10056;10676;9160;7990;7990;7990;7990;8403;8816;8678;8540;8540;8265;7990;0;10332;10332;9712;9092;9092;9092;9367;9642</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -3061,44 +3389,44 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>521465</t>
+          <t>1070883</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Студия</t>
+          <t>Апартаменты стандарт с 1 двуспальной кроватью</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2699</v>
+        <v>3675</v>
       </c>
       <c r="D44" t="n">
-        <v>8.9</v>
+        <v>9.6</v>
       </c>
       <c r="E44" t="n">
-        <v>173</v>
+        <v>336</v>
       </c>
       <c r="F44" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Полтавская улица, 5</t>
+          <t>Санкт-Петербург, Суворовский проспект, 65</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~7 мин. пешком</t>
+          <t>Чернышевская ~32 мин. пешком</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3109,11 +3437,19 @@
       <c r="K44" t="n">
         <v>0</v>
       </c>
-      <c r="L44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="inlineStr"/>
+        <v>8136</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>3675;4800;4800;5700;5700;5700;5700;6750;6750;6750;6750;6750;6750;6750;6750;7350;7350;6750;6750;6150;6150;6150;6150;6150;6750;6750;6150;7950;8550;12150;12150;12150;12150;7950;7950;7950;7950;12150;8505;7665;9750;8550;8550;9750;9750;12150;11550;7350;7350;7350;12150;12750;9450;13500;7950;7950;7950;9750;9750;10950</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -3121,44 +3457,44 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>784713</t>
+          <t>806761</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Апартаменты улучшенная студия с кроватью king size и балконом</t>
+          <t>Современная студия в 10 минутах пешком от метро пл. Мужества</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2990</v>
+        <v>3585</v>
       </c>
       <c r="D45" t="n">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>329</v>
+        <v>1516</v>
       </c>
       <c r="F45" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G45" t="n">
         <v>2</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Пулковское шоссе, 14с6</t>
+          <t>Санкт-Петербург, Политехническая улица, 6</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Звёздная ~17 мин. пешком</t>
+          <t>Площадь Мужества ~12 мин. пешком</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3169,11 +3505,19 @@
       <c r="K45" t="n">
         <v>0</v>
       </c>
-      <c r="L45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="inlineStr"/>
+        <v>6389</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>3585;3900;3900;4880;5860;4180;4180;4040;4320;4320;5300;5300;5020;5020;5020;5020;5020;5300;5300;5020;5020;5020;5020;5020;5300;5300;5020;7120;7120;7120;7120;8800;8800;7120;7120;7120;7120;7120;7820;7820;7120;7120;7120;7120;7120;8800;8800;7120;7120;7120;7120;7120;8800;8800;7120;7120;7120;8800;8800;10480</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -3181,44 +3525,44 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2085567</t>
+          <t>1562440</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Просторная студия с креслом</t>
+          <t>2-местная евро студия</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2577</v>
+        <v>4179</v>
       </c>
       <c r="D46" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="E46" t="n">
-        <v>433</v>
+        <v>280</v>
       </c>
       <c r="F46" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Энергетиков проспект, 8к2</t>
+          <t>Санкт-Петербург, Звенигородская улица, 6</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Ладожская ~13 мин. пешком</t>
+          <t>Звенигородская ~2 мин. пешком</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3229,11 +3573,19 @@
       <c r="K46" t="n">
         <v>0</v>
       </c>
-      <c r="L46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="inlineStr"/>
+        <v>7760</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>4179;4443;4644;5716;6252;5984;4711;4912;4912;4912;5850;5850;5247;5247;5649;5649;5649;6051;6051;5448;5850;5850;5649;5649;8832;8832;8028;8028;10574;10574;10976;10976;9368;8564;8564;8832;8832;10976;10976;10574;8296;8564;8832;8832;8564;9100;9368;8564;8832;9100;9100;9033;11378;10976;8765;8564;8832;8832;8832;9368</t>
+        </is>
+      </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -3241,44 +3593,44 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1012567</t>
+          <t>1775758</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Улучшенные апартаменты</t>
+          <t>Апартаменты с кухней</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4440</v>
+        <v>7649</v>
       </c>
       <c r="D47" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="E47" t="n">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="F47" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Садовая улица, 28-30к1</t>
+          <t>Санкт-Петербург, Лиговский проспект, 44</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Сенная площадь ~6 мин. пешком</t>
+          <t>Площадь Восстания ~6 мин. пешком</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3289,11 +3641,19 @@
       <c r="K47" t="n">
         <v>0</v>
       </c>
-      <c r="L47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="inlineStr"/>
+        <v>14902</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>7649;8249;8249;11999;12599;9749;8699;8699;8699;12899;12899;13499;12449;12449;12449;12449;12449;12449;12449;12449;12449;12449;12449;9449;12449;12449;12449;13949;21599;21599;21599;21599;21599;13949;13949;13949;13949;23099;23099;23099;23099;12899;16349;16349;16349;16349;16349;15599;15599;15599;15599;15599;22949;22949;22949;13949;13949;15149;15149;16649</t>
+        </is>
+      </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -3301,44 +3661,44 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1775758</t>
+          <t>1105851</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Апартаменты с кухней</t>
+          <t>Апартаменты студия комфорт</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>7649</v>
+        <v>6039</v>
       </c>
       <c r="D48" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E48" t="n">
-        <v>411</v>
+        <v>485</v>
       </c>
       <c r="F48" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Лиговский проспект, 44</t>
+          <t>Санкт-Петербург, Лиговский проспект, 29</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Площадь Восстания ~6 мин. пешком</t>
+          <t>Площадь Восстания ~7 мин. пешком</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3349,11 +3709,19 @@
       <c r="K48" t="n">
         <v>0</v>
       </c>
-      <c r="L48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="inlineStr"/>
+        <v>8863</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>6039;6710;5610;8925;9450;8925;5610;5610;5940;5940;7810;7810;5610;5940;8800;8800;7810;7810;9350;7040;6710;6710;7169;7169;9095;9095;7169;9095;10165;11550;11550;11550;11550;7597;9095;9095;9095;11770;11550;10858;10165;9630;11235;11770;10165;10165;10165;9095;9095;9095;9095;10165;11025;11025;9095;9095;9095;9630;9630;10165</t>
+        </is>
+      </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -3361,44 +3729,44 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1926972</t>
+          <t>731147</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Светлая студия в центре</t>
+          <t>Апартаменты стандарт</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4721</v>
+        <v>4410</v>
       </c>
       <c r="D49" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>199</v>
+        <v>119</v>
       </c>
       <c r="F49" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Гороховая улица, 30</t>
+          <t>Санкт-Петербург, Лиговский проспект, 84/2Б</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Сенная площадь ~5 мин. пешком</t>
+          <t>Лиговский проспект ~1 мин. пешком</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3409,11 +3777,19 @@
       <c r="K49" t="n">
         <v>0</v>
       </c>
-      <c r="L49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="inlineStr"/>
+        <v>7437</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>4410;4410;4410;4410;7245;7245;4410;4410;4410;9660;9660;9660;6195;6195;6195;6195;6773;6773;6773;6195;6510;6510;6510;6510;6510;6510;6195;6773;6773;12810;12810;12810;7560;7560;7560;7560;7560;7560;13860;13860;7560;7560;7560;7560;7560;7560;7560;7560;7560;7560;7560;7560;7560;7560;7560;7560;7560;7245;7245;7245</t>
+        </is>
+      </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -3421,44 +3797,44 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1464729</t>
+          <t>1713984</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Апартаменты стандарт</t>
+          <t>Улучшенные апартаменты с одной кроватью и мини-кухней</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2236</v>
+        <v>3770</v>
       </c>
       <c r="D50" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="E50" t="n">
-        <v>216</v>
+        <v>977</v>
       </c>
       <c r="F50" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G50" t="n">
         <v>2</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Марата улица, 56-58/29</t>
+          <t>Санкт-Петербург, Невский проспект, 90</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Лиговский проспект ~5 мин. пешком</t>
+          <t>Маяковская ~3 мин. пешком</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3469,11 +3845,19 @@
       <c r="K50" t="n">
         <v>0</v>
       </c>
-      <c r="L50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="inlineStr"/>
+        <v>8499</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>3770;3770;3770;5655;5655;5075;3770;3770;5510;5510;8845;9425;8265;8265;8265;8265;8265;9425;9425;8845;8845;8845;8845;8845;9135;9135;8265;8845;8845;12398;12398;11227;9230;8403;8403;8954;9505;10607;11364;9712;8403;8403;8403;8403;8816;9230;9092;8954;8954;8678;8403;9712;11020;11020;10262;9505;7990;9505;9780;10056</t>
+        </is>
+      </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -3481,44 +3865,44 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>803069</t>
+          <t>1720400</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Комфортная студия рядом с метро Площадь Мужества</t>
+          <t>Апартамент эконом с раздельными кроватями</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3347</v>
+        <v>2349</v>
       </c>
       <c r="D51" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>1516</v>
+        <v>627</v>
       </c>
       <c r="F51" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G51" t="n">
         <v>2</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Политехническая улица, 6</t>
+          <t>Санкт-Петербург, реки Фонтанки набережная, 87</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Площадь Мужества ~12 мин. пешком</t>
+          <t>Сенная площадь ~7 мин. пешком</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3529,11 +3913,19 @@
       <c r="K51" t="n">
         <v>0</v>
       </c>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
       <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="inlineStr"/>
+        <v>6664</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>2349;2320;2320;5220;5220;4785;2610;2320;3915;6090;6670;7250;6090;6090;6090;6090;6090;6670;6670;6090;6090;6090;7540;7540;0;0;0;0;0;8265;8265;7806;7347;6888;6888;6888;7576;8610;9642;8678;7026;7975;7576;7576;8265;8265;7714;9092;7576;7576;7026;7714;8954;7714;7026;6888;7026;7163;0;0</t>
+        </is>
+      </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
           <t>Открыть</t>
@@ -3541,7 +3933,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-05-05 09:16</t>
+          <t>2026-05-05 11:28</t>
         </is>
       </c>
     </row>
